--- a/Marini_iDigBio_306museums_coord_with_country_for518Map.xlsx
+++ b/Marini_iDigBio_306museums_coord_with_country_for518Map.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yiru Cheng\Dropbox\2022 Academia Sinica\Research\data\Egg\Global egg collection\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yiru Cheng\Dropbox\2022 Academia Sinica\non-research\2026鳥蛋展覽\全球鳥蛋博物館地圖\antigravity\global-egg-dataset-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5582A43-BE1C-4439-96F6-42404FD722BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9DEBE0F-4D95-4585-9FF0-0CAFC59988FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$306</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$307</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3006,6 +3006,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Marini+iDigBio"/>
       <sheetName val="stats-211Museum"/>
@@ -9184,7 +9187,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -9283,7 +9286,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="75" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -9316,7 +9319,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -9349,7 +9352,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -9415,7 +9418,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -9448,7 +9451,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -9481,7 +9484,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -9514,7 +9517,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -9578,7 +9581,7 @@
       </c>
       <c r="J13" s="12"/>
     </row>
-    <row r="14" spans="1:10" ht="75" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -9611,7 +9614,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -9644,7 +9647,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -9677,7 +9680,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -9710,7 +9713,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -9743,7 +9746,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -9776,7 +9779,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -9809,7 +9812,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -9842,7 +9845,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -9875,7 +9878,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -9908,7 +9911,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -9941,7 +9944,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -9974,7 +9977,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -10007,7 +10010,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="90" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -10040,7 +10043,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="120" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -10073,7 +10076,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -10106,7 +10109,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="75" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -10139,7 +10142,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -10172,7 +10175,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -10205,7 +10208,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -10238,7 +10241,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -10271,7 +10274,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -10304,7 +10307,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="75" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -10337,7 +10340,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -10370,7 +10373,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -10403,7 +10406,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="75" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -10436,7 +10439,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -10469,7 +10472,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="75" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -10502,7 +10505,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -10535,7 +10538,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="90" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -10568,7 +10571,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>48</v>
       </c>
@@ -10601,7 +10604,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>49</v>
       </c>
@@ -10634,7 +10637,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>50</v>
       </c>
@@ -10667,7 +10670,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -10700,7 +10703,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>41</v>
       </c>
@@ -10733,7 +10736,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -10766,7 +10769,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>52</v>
       </c>
@@ -10799,7 +10802,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -10832,7 +10835,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>54</v>
       </c>
@@ -10865,7 +10868,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>55</v>
       </c>
@@ -10929,7 +10932,7 @@
       </c>
       <c r="J54" s="12"/>
     </row>
-    <row r="55" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>57</v>
       </c>
@@ -10962,7 +10965,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>58</v>
       </c>
@@ -10995,7 +10998,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>24</v>
       </c>
@@ -11028,7 +11031,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>59</v>
       </c>
@@ -11061,7 +11064,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>60</v>
       </c>
@@ -11094,7 +11097,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>61</v>
       </c>
@@ -11127,7 +11130,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>62</v>
       </c>
@@ -11160,7 +11163,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>63</v>
       </c>
@@ -11193,7 +11196,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="75" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>64</v>
       </c>
@@ -11226,7 +11229,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>65</v>
       </c>
@@ -11259,7 +11262,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>66</v>
       </c>
@@ -11292,7 +11295,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>67</v>
       </c>
@@ -11325,7 +11328,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>68</v>
       </c>
@@ -11358,7 +11361,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>69</v>
       </c>
@@ -11391,7 +11394,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="180" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:10" ht="60" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>70</v>
       </c>
@@ -11424,7 +11427,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="75" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>71</v>
       </c>
@@ -11457,7 +11460,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>72</v>
       </c>
@@ -11490,7 +11493,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>73</v>
       </c>
@@ -11523,7 +11526,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="75" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>74</v>
       </c>
@@ -11556,7 +11559,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>75</v>
       </c>
@@ -11589,7 +11592,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>76</v>
       </c>
@@ -11622,7 +11625,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="75" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>77</v>
       </c>
@@ -11655,7 +11658,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>78</v>
       </c>
@@ -11688,7 +11691,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="105" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>79</v>
       </c>
@@ -11711,8 +11714,7 @@
         <v>448</v>
       </c>
       <c r="H78" s="6">
-        <f>VLOOKUP(A78, '[1]Marini+iDigBio'!$D$2:$J$306, 7, FALSE)</f>
-        <v>4396.666666666667</v>
+        <v>23288</v>
       </c>
       <c r="I78">
         <v>1</v>
@@ -11721,7 +11723,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>80</v>
       </c>
@@ -11754,7 +11756,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>81</v>
       </c>
@@ -11787,7 +11789,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>82</v>
       </c>
@@ -11851,7 +11853,7 @@
       </c>
       <c r="J82" s="12"/>
     </row>
-    <row r="83" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>84</v>
       </c>
@@ -11884,7 +11886,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:10" ht="45" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>85</v>
       </c>
@@ -11917,7 +11919,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>86</v>
       </c>
@@ -11950,7 +11952,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>87</v>
       </c>
@@ -11983,7 +11985,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>88</v>
       </c>
@@ -12016,7 +12018,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="75" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>89</v>
       </c>
@@ -12049,7 +12051,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>90</v>
       </c>
@@ -12082,7 +12084,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>91</v>
       </c>
@@ -12115,7 +12117,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>92</v>
       </c>
@@ -12148,7 +12150,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="75" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>93</v>
       </c>
@@ -12181,7 +12183,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="75" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>94</v>
       </c>
@@ -12247,7 +12249,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>96</v>
       </c>
@@ -12280,7 +12282,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>97</v>
       </c>
@@ -12313,7 +12315,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>98</v>
       </c>
@@ -12346,7 +12348,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>99</v>
       </c>
@@ -12412,7 +12414,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>24</v>
       </c>
@@ -12445,7 +12447,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>101</v>
       </c>
@@ -12478,7 +12480,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>102</v>
       </c>
@@ -12511,7 +12513,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>103</v>
       </c>
@@ -12575,7 +12577,7 @@
       </c>
       <c r="J104" s="12"/>
     </row>
-    <row r="105" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>105</v>
       </c>
@@ -12608,7 +12610,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>106</v>
       </c>
@@ -12641,7 +12643,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>107</v>
       </c>
@@ -12674,7 +12676,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>108</v>
       </c>
@@ -12707,7 +12709,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="120" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:10" ht="45" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>109</v>
       </c>
@@ -12740,7 +12742,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>110</v>
       </c>
@@ -12773,7 +12775,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>111</v>
       </c>
@@ -12839,7 +12841,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>113</v>
       </c>
@@ -12872,7 +12874,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>114</v>
       </c>
@@ -12905,7 +12907,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="105" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>115</v>
       </c>
@@ -12969,7 +12971,7 @@
       </c>
       <c r="J116" s="12"/>
     </row>
-    <row r="117" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>117</v>
       </c>
@@ -13002,7 +13004,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="75" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>118</v>
       </c>
@@ -13035,7 +13037,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>119</v>
       </c>
@@ -13068,7 +13070,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>120</v>
       </c>
@@ -13101,7 +13103,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="75" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>121</v>
       </c>
@@ -13134,7 +13136,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>122</v>
       </c>
@@ -13167,7 +13169,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>123</v>
       </c>
@@ -13200,7 +13202,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>124</v>
       </c>
@@ -13233,7 +13235,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>125</v>
       </c>
@@ -13266,7 +13268,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>126</v>
       </c>
@@ -13299,7 +13301,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>127</v>
       </c>
@@ -13332,7 +13334,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>128</v>
       </c>
@@ -13365,7 +13367,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>129</v>
       </c>
@@ -13431,7 +13433,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>131</v>
       </c>
@@ -13464,7 +13466,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>132</v>
       </c>
@@ -13530,7 +13532,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:10" ht="45" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>134</v>
       </c>
@@ -13563,7 +13565,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>135</v>
       </c>
@@ -13596,7 +13598,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>136</v>
       </c>
@@ -13629,7 +13631,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>9</v>
       </c>
@@ -13662,7 +13664,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>137</v>
       </c>
@@ -13695,7 +13697,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>138</v>
       </c>
@@ -13728,7 +13730,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>139</v>
       </c>
@@ -13761,7 +13763,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="75" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>9</v>
       </c>
@@ -13794,7 +13796,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="75" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>140</v>
       </c>
@@ -13860,7 +13862,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>142</v>
       </c>
@@ -13893,7 +13895,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>13</v>
       </c>
@@ -13926,7 +13928,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>143</v>
       </c>
@@ -13959,7 +13961,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>144</v>
       </c>
@@ -13992,7 +13994,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>145</v>
       </c>
@@ -14025,7 +14027,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>146</v>
       </c>
@@ -14091,7 +14093,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="151" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>148</v>
       </c>
@@ -14124,7 +14126,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="152" spans="1:10" ht="75" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>149</v>
       </c>
@@ -14188,7 +14190,7 @@
       </c>
       <c r="J153" s="12"/>
     </row>
-    <row r="154" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>151</v>
       </c>
@@ -14221,7 +14223,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="155" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>152</v>
       </c>
@@ -14254,7 +14256,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="156" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>153</v>
       </c>
@@ -14287,7 +14289,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>154</v>
       </c>
@@ -14320,7 +14322,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="158" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>155</v>
       </c>
@@ -14353,7 +14355,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="159" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>156</v>
       </c>
@@ -14386,7 +14388,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="160" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>157</v>
       </c>
@@ -14419,7 +14421,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="161" spans="1:10" ht="75" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>158</v>
       </c>
@@ -14452,7 +14454,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="75" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>159</v>
       </c>
@@ -14485,7 +14487,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="163" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>160</v>
       </c>
@@ -14549,7 +14551,7 @@
       </c>
       <c r="J164" s="12"/>
     </row>
-    <row r="165" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>162</v>
       </c>
@@ -14582,7 +14584,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="166" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>163</v>
       </c>
@@ -14615,7 +14617,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="167" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>164</v>
       </c>
@@ -14648,7 +14650,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="168" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>165</v>
       </c>
@@ -14681,7 +14683,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="169" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>166</v>
       </c>
@@ -14714,7 +14716,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="170" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>167</v>
       </c>
@@ -14747,7 +14749,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="171" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>168</v>
       </c>
@@ -14780,7 +14782,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="172" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>169</v>
       </c>
@@ -14813,7 +14815,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="173" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>170</v>
       </c>
@@ -14846,7 +14848,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="174" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>171</v>
       </c>
@@ -14879,7 +14881,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="175" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>172</v>
       </c>
@@ -14912,7 +14914,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="176" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>173</v>
       </c>
@@ -14945,7 +14947,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>174</v>
       </c>
@@ -14978,7 +14980,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>175</v>
       </c>
@@ -15042,7 +15044,7 @@
       </c>
       <c r="J179" s="12"/>
     </row>
-    <row r="180" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>177</v>
       </c>
@@ -15075,7 +15077,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="181" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>178</v>
       </c>
@@ -15108,7 +15110,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="182" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>179</v>
       </c>
@@ -15141,7 +15143,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="183" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>180</v>
       </c>
@@ -15174,7 +15176,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="184" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>181</v>
       </c>
@@ -15238,7 +15240,7 @@
       </c>
       <c r="J185" s="12"/>
     </row>
-    <row r="186" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>183</v>
       </c>
@@ -15271,7 +15273,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="187" spans="1:10" ht="75" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>184</v>
       </c>
@@ -15304,7 +15306,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="188" spans="1:10" ht="75" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>185</v>
       </c>
@@ -15337,7 +15339,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="189" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>186</v>
       </c>
@@ -15370,7 +15372,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="190" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>187</v>
       </c>
@@ -15403,7 +15405,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="191" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>39</v>
       </c>
@@ -15436,7 +15438,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="192" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>188</v>
       </c>
@@ -15500,7 +15502,7 @@
       </c>
       <c r="J193" s="12"/>
     </row>
-    <row r="194" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
         <v>190</v>
       </c>
@@ -15533,7 +15535,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="195" spans="1:10" ht="90" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
         <v>191</v>
       </c>
@@ -15566,7 +15568,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="196" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
         <v>192</v>
       </c>
@@ -15599,7 +15601,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="197" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
         <v>193</v>
       </c>
@@ -15665,7 +15667,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="199" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
         <v>195</v>
       </c>
@@ -15698,7 +15700,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="200" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
         <v>196</v>
       </c>
@@ -15731,7 +15733,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="201" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
         <v>197</v>
       </c>
@@ -15764,7 +15766,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="202" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
         <v>198</v>
       </c>
@@ -15828,7 +15830,7 @@
       </c>
       <c r="J203" s="12"/>
     </row>
-    <row r="204" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
         <v>200</v>
       </c>
@@ -15861,7 +15863,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="205" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
         <v>201</v>
       </c>
@@ -15925,7 +15927,7 @@
       </c>
       <c r="J206" s="12"/>
     </row>
-    <row r="207" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
         <v>203</v>
       </c>
@@ -15958,7 +15960,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="208" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
         <v>204</v>
       </c>
@@ -15991,7 +15993,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="209" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
         <v>205</v>
       </c>
@@ -16024,7 +16026,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="210" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
         <v>206</v>
       </c>
@@ -16057,7 +16059,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="211" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A211" s="2" t="s">
         <v>452</v>
       </c>
@@ -16154,7 +16156,7 @@
       </c>
       <c r="J213" s="12"/>
     </row>
-    <row r="214" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:10" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A214" s="2" t="s">
         <v>455</v>
       </c>
@@ -16187,7 +16189,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="215" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A215" s="2" t="s">
         <v>456</v>
       </c>
@@ -16220,7 +16222,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="216" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A216" s="2" t="s">
         <v>457</v>
       </c>
@@ -16253,7 +16255,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="217" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A217" s="2" t="s">
         <v>458</v>
       </c>
@@ -16286,7 +16288,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="218" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A218" s="2" t="s">
         <v>459</v>
       </c>
@@ -16319,7 +16321,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="219" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A219" s="2" t="s">
         <v>460</v>
       </c>
@@ -16352,7 +16354,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="220" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:10" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A220" s="2" t="s">
         <v>461</v>
       </c>
@@ -16385,7 +16387,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="221" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A221" s="2" t="s">
         <v>462</v>
       </c>
@@ -16418,7 +16420,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="222" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A222" s="2" t="s">
         <v>463</v>
       </c>
@@ -16451,7 +16453,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="223" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A223" s="2" t="s">
         <v>464</v>
       </c>
@@ -16484,7 +16486,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="224" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A224" s="2" t="s">
         <v>465</v>
       </c>
@@ -16550,7 +16552,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="226" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A226" s="2" t="s">
         <v>467</v>
       </c>
@@ -16583,7 +16585,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="227" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A227" s="2" t="s">
         <v>468</v>
       </c>
@@ -16616,7 +16618,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="228" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A228" s="2" t="s">
         <v>469</v>
       </c>
@@ -16649,7 +16651,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="229" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A229" s="2" t="s">
         <v>470</v>
       </c>
@@ -16682,7 +16684,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="230" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A230" s="2" t="s">
         <v>471</v>
       </c>
@@ -16715,7 +16717,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="231" spans="1:10" ht="75" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A231" s="2" t="s">
         <v>472</v>
       </c>
@@ -16748,7 +16750,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="232" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A232" s="2" t="s">
         <v>473</v>
       </c>
@@ -16781,7 +16783,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="233" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A233" s="2" t="s">
         <v>474</v>
       </c>
@@ -16845,7 +16847,7 @@
       </c>
       <c r="J234" s="12"/>
     </row>
-    <row r="235" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A235" s="2" t="s">
         <v>476</v>
       </c>
@@ -16878,7 +16880,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="236" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A236" s="2" t="s">
         <v>477</v>
       </c>
@@ -16911,7 +16913,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="237" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A237" s="2" t="s">
         <v>478</v>
       </c>
@@ -17006,7 +17008,7 @@
       </c>
       <c r="J239" s="12"/>
     </row>
-    <row r="240" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A240" s="2" t="s">
         <v>481</v>
       </c>
@@ -17039,7 +17041,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="241" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A241" s="2" t="s">
         <v>482</v>
       </c>
@@ -17072,7 +17074,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="242" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A242" s="2" t="s">
         <v>483</v>
       </c>
@@ -17105,7 +17107,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="243" spans="1:10" ht="75" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A243" s="2" t="s">
         <v>158</v>
       </c>
@@ -17171,7 +17173,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="245" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A245" s="2" t="s">
         <v>485</v>
       </c>
@@ -17204,7 +17206,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="246" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A246" s="2" t="s">
         <v>486</v>
       </c>
@@ -17237,7 +17239,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="247" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A247" s="2" t="s">
         <v>487</v>
       </c>
@@ -17270,7 +17272,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="248" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A248" s="2" t="s">
         <v>488</v>
       </c>
@@ -17303,7 +17305,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="249" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A249" s="2" t="s">
         <v>489</v>
       </c>
@@ -17367,7 +17369,7 @@
       </c>
       <c r="J250" s="12"/>
     </row>
-    <row r="251" spans="1:10" ht="75" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:10" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A251" s="2" t="s">
         <v>491</v>
       </c>
@@ -17400,7 +17402,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="252" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A252" s="2" t="s">
         <v>492</v>
       </c>
@@ -17433,7 +17435,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="253" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A253" s="2" t="s">
         <v>493</v>
       </c>
@@ -17466,7 +17468,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="254" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A254" s="2" t="s">
         <v>494</v>
       </c>
@@ -17499,7 +17501,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="255" spans="1:10" ht="75" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A255" s="2" t="s">
         <v>495</v>
       </c>
@@ -17532,7 +17534,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="256" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A256" s="2" t="s">
         <v>496</v>
       </c>
@@ -17565,7 +17567,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="257" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A257" s="2" t="s">
         <v>497</v>
       </c>
@@ -17598,7 +17600,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="258" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A258" s="2" t="s">
         <v>13</v>
       </c>
@@ -17631,7 +17633,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="259" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A259" s="2" t="s">
         <v>498</v>
       </c>
@@ -17664,7 +17666,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="260" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A260" s="2" t="s">
         <v>499</v>
       </c>
@@ -17728,7 +17730,7 @@
       </c>
       <c r="J261" s="12"/>
     </row>
-    <row r="262" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A262" s="2" t="s">
         <v>501</v>
       </c>
@@ -17761,7 +17763,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="263" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A263" s="2" t="s">
         <v>502</v>
       </c>
@@ -17794,7 +17796,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="264" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A264" s="2" t="s">
         <v>503</v>
       </c>
@@ -17827,7 +17829,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="265" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A265" s="2" t="s">
         <v>504</v>
       </c>
@@ -17860,7 +17862,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="266" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A266" s="2" t="s">
         <v>505</v>
       </c>
@@ -17893,7 +17895,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="267" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A267" s="2" t="s">
         <v>506</v>
       </c>
@@ -17926,7 +17928,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="268" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A268" s="2" t="s">
         <v>507</v>
       </c>
@@ -17959,7 +17961,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="269" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A269" s="2" t="s">
         <v>508</v>
       </c>
@@ -17992,7 +17994,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="270" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A270" s="2" t="s">
         <v>509</v>
       </c>
@@ -18025,7 +18027,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="271" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A271" s="2" t="s">
         <v>510</v>
       </c>
@@ -18058,7 +18060,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="272" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A272" s="2" t="s">
         <v>41</v>
       </c>
@@ -18091,7 +18093,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="273" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A273" s="2" t="s">
         <v>511</v>
       </c>
@@ -18124,7 +18126,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="274" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A274" s="2" t="s">
         <v>512</v>
       </c>
@@ -18157,7 +18159,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="275" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A275" s="2" t="s">
         <v>513</v>
       </c>
@@ -18190,7 +18192,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="276" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A276" s="2" t="s">
         <v>514</v>
       </c>
@@ -18223,7 +18225,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="277" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A277" s="2" t="s">
         <v>515</v>
       </c>
@@ -18256,7 +18258,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="278" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:10" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A278" s="2" t="s">
         <v>516</v>
       </c>
@@ -18289,7 +18291,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="279" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A279" s="2" t="s">
         <v>517</v>
       </c>
@@ -18353,7 +18355,7 @@
       </c>
       <c r="J280" s="12"/>
     </row>
-    <row r="281" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A281" s="2" t="s">
         <v>519</v>
       </c>
@@ -18386,7 +18388,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="282" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A282" s="2" t="s">
         <v>520</v>
       </c>
@@ -18419,7 +18421,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="283" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:10" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A283" s="2" t="s">
         <v>521</v>
       </c>
@@ -18452,7 +18454,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="284" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A284" s="2" t="s">
         <v>522</v>
       </c>
@@ -18516,7 +18518,7 @@
       </c>
       <c r="J285" s="12"/>
     </row>
-    <row r="286" spans="1:10" ht="75" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A286" s="2" t="s">
         <v>524</v>
       </c>
@@ -18611,7 +18613,7 @@
       </c>
       <c r="J288" s="12"/>
     </row>
-    <row r="289" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A289" s="2" t="s">
         <v>527</v>
       </c>
@@ -18675,7 +18677,7 @@
       </c>
       <c r="J290" s="12"/>
     </row>
-    <row r="291" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A291" s="2" t="s">
         <v>529</v>
       </c>
@@ -18708,7 +18710,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="292" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A292" s="2" t="s">
         <v>530</v>
       </c>
@@ -18741,7 +18743,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="293" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A293" s="2" t="s">
         <v>531</v>
       </c>
@@ -18774,7 +18776,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="294" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A294" s="2" t="s">
         <v>532</v>
       </c>
@@ -18807,7 +18809,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="295" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A295" s="2" t="s">
         <v>533</v>
       </c>
@@ -18871,7 +18873,7 @@
       </c>
       <c r="J296" s="12"/>
     </row>
-    <row r="297" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A297" s="2" t="s">
         <v>535</v>
       </c>
@@ -18937,7 +18939,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="299" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A299" s="2" t="s">
         <v>537</v>
       </c>
@@ -19001,7 +19003,7 @@
       </c>
       <c r="J300" s="12"/>
     </row>
-    <row r="301" spans="1:10" ht="75" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:10" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A301" s="2" t="s">
         <v>539</v>
       </c>
@@ -19034,7 +19036,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="302" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:10" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A302" s="3" t="s">
         <v>540</v>
       </c>
@@ -19067,7 +19069,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="303" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A303" s="4" t="s">
         <v>541</v>
       </c>
@@ -19100,7 +19102,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="304" spans="1:10" ht="120" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:10" ht="45" x14ac:dyDescent="0.45">
       <c r="A304" s="4" t="s">
         <v>542</v>
       </c>
@@ -19122,10 +19124,6 @@
       <c r="G304" t="s">
         <v>447</v>
       </c>
-      <c r="H304" s="6">
-        <f>VLOOKUP(A304, '[1]Marini+iDigBio'!$D$2:$J$306, 7, FALSE)</f>
-        <v>0</v>
-      </c>
       <c r="I304" t="e">
         <v>#N/A</v>
       </c>
@@ -19133,7 +19131,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="305" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A305" s="4" t="s">
         <v>543</v>
       </c>
@@ -19155,10 +19153,6 @@
       <c r="G305" t="s">
         <v>447</v>
       </c>
-      <c r="H305" s="6">
-        <f>VLOOKUP(A305, '[1]Marini+iDigBio'!$D$2:$J$306, 7, FALSE)</f>
-        <v>0</v>
-      </c>
       <c r="I305" t="e">
         <v>#N/A</v>
       </c>
@@ -19166,7 +19160,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="306" spans="1:10" ht="60" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A306" s="4" t="s">
         <v>544</v>
       </c>
@@ -19187,10 +19181,6 @@
       </c>
       <c r="G306" t="s">
         <v>447</v>
-      </c>
-      <c r="H306" s="6">
-        <f>VLOOKUP(A306, '[1]Marini+iDigBio'!$D$2:$J$306, 7, FALSE)</f>
-        <v>0</v>
       </c>
       <c r="I306" t="e">
         <v>#N/A</v>
@@ -21311,7 +21301,7 @@
       <c r="J1000" s="12"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I306" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I307" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="J2" r:id="rId1" display="https://www.nhm.ac.uk/" xr:uid="{305EF9E5-9F84-4710-A3B4-BAAF1B556BF1}"/>

--- a/Marini_iDigBio_306museums_coord_with_country_for518Map.xlsx
+++ b/Marini_iDigBio_306museums_coord_with_country_for518Map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yiru Cheng\Dropbox\2022 Academia Sinica\non-research\2026鳥蛋展覽\全球鳥蛋博物館地圖\antigravity\global-egg-dataset-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9DEBE0F-4D95-4585-9FF0-0CAFC59988FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC141DE-BB60-4A60-84A0-0243F1CE1286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7680" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1821" uniqueCount="924">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1833" uniqueCount="940">
   <si>
     <t>Museum</t>
   </si>
@@ -2057,9 +2057,6 @@
     <t>https://www.sbcounty.gov/museum</t>
   </si>
   <si>
-    <t>https://www.naturwissenschaften.uni-halle.de</t>
-  </si>
-  <si>
     <t>https://www.fieldmuseum.org</t>
   </si>
   <si>
@@ -2072,12 +2069,6 @@
     <t>https://www.zin.ru</t>
   </si>
   <si>
-    <t>https://www.ville-ge.ch/mhng</t>
-  </si>
-  <si>
-    <t>https://snm.ku.dk</t>
-  </si>
-  <si>
     <t>https://www.amnh.org</t>
   </si>
   <si>
@@ -2099,9 +2090,6 @@
     <t>https://www.liverpoolmuseums.org.uk/world-museum</t>
   </si>
   <si>
-    <t>https://www.oxfordshire.gov.uk/residents/leisure-and-culture/museums</t>
-  </si>
-  <si>
     <t>https://www.uwgb.edu</t>
   </si>
   <si>
@@ -2123,51 +2111,30 @@
     <t>https://www.naturkundemuseum-bw.de</t>
   </si>
   <si>
-    <t>https://www.lwl-naturkundemuseum.de</t>
-  </si>
-  <si>
-    <t>https://www.nhm.uio.no</t>
-  </si>
-  <si>
     <t>https://www.glasgowlife.org.uk/museums</t>
   </si>
   <si>
     <t>https://greatnorthmuseum.org.uk</t>
   </si>
   <si>
-    <t>https://www.brightonmuseums.org.uk/booth</t>
-  </si>
-  <si>
     <t>https://www.sbnature.org</t>
   </si>
   <si>
-    <t>https://carnegiemuseums.org/museums/natural-history</t>
-  </si>
-  <si>
     <t>https://www.ditsong.org.za</t>
   </si>
   <si>
     <t>https://www.nmbe.ch</t>
   </si>
   <si>
-    <t>https://museum.nantes.fr</t>
-  </si>
-  <si>
     <t>https://museum.wales</t>
   </si>
   <si>
     <t>https://www.museum.zoo.cam.ac.uk</t>
   </si>
   <si>
-    <t>https://www.nhmbulawayo.ac.zw</t>
-  </si>
-  <si>
     <t>https://www.calacademy.org</t>
   </si>
   <si>
-    <t>https://www.museumheineanum.de</t>
-  </si>
-  <si>
     <t>https://www.samuseum.sa.gov.au</t>
   </si>
   <si>
@@ -2204,9 +2171,6 @@
     <t>https://www.biologie.uni-hamburg.de/en/forschung/sammlungen-und-garten/centrum-fuer-naturkunde.html</t>
   </si>
   <si>
-    <t>https://www.naturkundemuseum.potsdam.de</t>
-  </si>
-  <si>
     <t>https://www.burkemuseum.org</t>
   </si>
   <si>
@@ -2222,9 +2186,6 @@
     <t>https://www.illinoisstatemuseum.org</t>
   </si>
   <si>
-    <t>https://research.net.osu.edu/portal/museums</t>
-  </si>
-  <si>
     <t>https://www.dmns.org</t>
   </si>
   <si>
@@ -2237,18 +2198,12 @@
     <t>https://www.mueritzeum.de</t>
   </si>
   <si>
-    <t>https://www.nature.ca</t>
-  </si>
-  <si>
     <t>https://www.charlestonmuseum.org</t>
   </si>
   <si>
     <t>https://samnoblemuseum.ou.edu</t>
   </si>
   <si>
-    <t>https://www.biologiezentrum.at</t>
-  </si>
-  <si>
     <t>https://www.tulliehouse.co.uk</t>
   </si>
   <si>
@@ -2261,12 +2216,6 @@
     <t>https://www.theherbert.org</t>
   </si>
   <si>
-    <t>https://www.muzeumkomensky.cz</t>
-  </si>
-  <si>
-    <t>https://loodusmuuseum.ee</t>
-  </si>
-  <si>
     <t>https://www.naturkunde-museum-coburg.de</t>
   </si>
   <si>
@@ -2279,81 +2228,48 @@
     <t>https://www.tulsazoo.org</t>
   </si>
   <si>
-    <t>https://www.aquazoo.de</t>
-  </si>
-  <si>
     <t>https://www.uib.no/universitetsmuseet</t>
   </si>
   <si>
     <t>https://www.naturundmensch.de</t>
   </si>
   <si>
-    <t>https://www.ni.is</t>
-  </si>
-  <si>
-    <t>https://www.msn.univr.it</t>
-  </si>
-  <si>
     <t>https://mlbean.byu.edu</t>
   </si>
   <si>
     <t>https://www.bristolmuseums.org.uk</t>
   </si>
   <si>
-    <t>https://www.mz.usp.br</t>
-  </si>
-  <si>
     <t>https://www.unr.edu</t>
   </si>
   <si>
     <t>https://www.saffronwaldenmuseum.org</t>
   </si>
   <si>
-    <t>https://www.uni-greifswald.de/en/university/about-us/museums</t>
-  </si>
-  <si>
     <t>https://www.mpm.edu</t>
   </si>
   <si>
-    <t>https://royalbcmuseum.bc.ca</t>
-  </si>
-  <si>
     <t>https://www.vt.edu</t>
   </si>
   <si>
-    <t>https://www.annistonmuseum.org</t>
-  </si>
-  <si>
     <t>https://www.cmnh.org</t>
   </si>
   <si>
-    <t>https://www.musees.strasbourg.eu/musees/musee-zoologique</t>
-  </si>
-  <si>
     <t>https://www.oumnh.ox.ac.uk</t>
   </si>
   <si>
-    <t>https://www.ne.ch/musee-histoire-naturelle</t>
-  </si>
-  <si>
     <t>https://biodiversity.ku.edu</t>
   </si>
   <si>
     <t>https://www.birds.cornell.edu</t>
   </si>
   <si>
-    <t>https://www.durbannaturalsciencemuseum.org.za</t>
-  </si>
-  <si>
     <t>https://www.museum.toulouse.fr</t>
   </si>
   <si>
     <t>https://www.museum.qld.gov.au</t>
   </si>
   <si>
-    <t>https://www.zoology.ubc.ca/museum</t>
-  </si>
-  <si>
     <t>https://uit.no/museum</t>
   </si>
   <si>
@@ -2369,9 +2285,6 @@
     <t>https://www.africamuseum.be</t>
   </si>
   <si>
-    <t>https://www.utu.fi/en/research/infrastructure/zoological-museum</t>
-  </si>
-  <si>
     <t>https://www.rammuseum.org.uk</t>
   </si>
   <si>
@@ -2417,15 +2330,9 @@
     <t>https://www.aucklandmuseum.com</t>
   </si>
   <si>
-    <t>https://www.museumamschoelerberg.de</t>
-  </si>
-  <si>
     <t>https://www.ccmuseum.com</t>
   </si>
   <si>
-    <t>https://www.uc.pt/fctuc/museus/museu-de-zoologia</t>
-  </si>
-  <si>
     <t>https://www.tepapa.govt.nz</t>
   </si>
   <si>
@@ -2453,48 +2360,24 @@
     <t>https://mnch.uoregon.edu</t>
   </si>
   <si>
-    <t>https://www.pollichia.de/museen/pfalzmuseum</t>
-  </si>
-  <si>
-    <t>https://www.lausanne.ch/musee-de-zoologie</t>
-  </si>
-  <si>
-    <t>https://www.shropshiremuseums.co.uk</t>
-  </si>
-  <si>
     <t>https://www.arizona.edu</t>
   </si>
   <si>
-    <t>https://www.landesmuseum-mainz.de</t>
-  </si>
-  <si>
     <t>https://www.mos.org</t>
   </si>
   <si>
-    <t>https://gamtostyrimai.vdu.lt</t>
-  </si>
-  <si>
-    <t>https://steinhardt.museum.tau.ac.il</t>
-  </si>
-  <si>
     <t>https://www.qvmag.tas.gov.au</t>
   </si>
   <si>
     <t>https://www.zsm.mwn.de</t>
   </si>
   <si>
-    <t>https://museum.aschaffenburg.de</t>
-  </si>
-  <si>
     <t>https://www.lillo.org.ar</t>
   </si>
   <si>
     <t>https://www.muzeumbardejov.sk</t>
   </si>
   <si>
-    <t>https://www.zoologicalmuseum.uzh.ch</t>
-  </si>
-  <si>
     <t>https://biodiversity.uconn.edu</t>
   </si>
   <si>
@@ -2537,12 +2420,6 @@
     <t>https://www.adams.edu</t>
   </si>
   <si>
-    <t>https://www.hazu.hr/hr/zavod-za-ornitologiju</t>
-  </si>
-  <si>
-    <t>https://naturkundemuseum.erfurt.de</t>
-  </si>
-  <si>
     <t>https://www.baylor.edu/mayborn</t>
   </si>
   <si>
@@ -2561,9 +2438,6 @@
     <t>https://www.uni-tuebingen.de</t>
   </si>
   <si>
-    <t>https://www.hetnatuurmuseum.nl</t>
-  </si>
-  <si>
     <t>https://www.bates.edu</t>
   </si>
   <si>
@@ -2582,9 +2456,6 @@
     <t>https://www.museocostarica.go.cr</t>
   </si>
   <si>
-    <t>https://www.oxy.edu/academics/areas-of-study/biology/moore-lab-zoology</t>
-  </si>
-  <si>
     <t>https://research.utep.edu/biodiversity</t>
   </si>
   <si>
@@ -2603,15 +2474,9 @@
     <t>https://www.tmag.tas.gov.au</t>
   </si>
   <si>
-    <t>https://www.zzpsnv.rs</t>
-  </si>
-  <si>
     <t>https://www.zzps.rs</t>
   </si>
   <si>
-    <t>https://www.zmmu.msu.ru</t>
-  </si>
-  <si>
     <t>https://www.coe.edu</t>
   </si>
   <si>
@@ -2627,9 +2492,6 @@
     <t>https://museum.novascotia.ca</t>
   </si>
   <si>
-    <t>https://www.msn.unipi.it</t>
-  </si>
-  <si>
     <t>https://www.fsu.edu</t>
   </si>
   <si>
@@ -2648,21 +2510,9 @@
     <t>https://www.manitobamuseum.ca</t>
   </si>
   <si>
-    <t>https://www.museodizoologia.it</t>
-  </si>
-  <si>
     <t>https://www.utm.edu</t>
   </si>
   <si>
-    <t>https://www.natuurmuseumfriesland.nl</t>
-  </si>
-  <si>
-    <t>https://www.museu-goeldi.br</t>
-  </si>
-  <si>
-    <t>https://zoology.muohio.edu</t>
-  </si>
-  <si>
     <t>https://www.mnhn.lu</t>
   </si>
   <si>
@@ -2681,9 +2531,6 @@
     <t>https://www.fortworthmuseum.org</t>
   </si>
   <si>
-    <t>https://www.santafe.gob.ar/museoflorentino</t>
-  </si>
-  <si>
     <t>https://www.calstate.edu</t>
   </si>
   <si>
@@ -2708,9 +2555,6 @@
     <t>https://www.colostate.edu</t>
   </si>
   <si>
-    <t>https://museos.ucr.ac.cr/zoologia</t>
-  </si>
-  <si>
     <t>https://www.mauritianum.de</t>
   </si>
   <si>
@@ -2729,9 +2573,6 @@
     <t>https://www.sdstate.edu</t>
   </si>
   <si>
-    <t>https://www.museum.bamberg.de</t>
-  </si>
-  <si>
     <t>https://www.muzeumkarkonoskie.pl</t>
   </si>
   <si>
@@ -2741,87 +2582,294 @@
     <t>https://www.mncn.csic.es</t>
   </si>
   <si>
-    <t>https://www.isprambiente.gov.it</t>
-  </si>
-  <si>
-    <t>https://www.ib.unam.mx/colecciones</t>
-  </si>
-  <si>
     <t>https://www.tatmuseum.ru</t>
   </si>
   <si>
     <t>https://www.ntnu.no/vitenskapsmuseet</t>
   </si>
   <si>
-    <t>https://www.pucrs.br/museudecencias</t>
-  </si>
-  <si>
-    <t>https://www.bpn.com.pl</t>
-  </si>
-  <si>
     <t>https://www.aquasis.org</t>
   </si>
   <si>
-    <t>https://www.fzb.rs.gov.br</t>
-  </si>
-  <si>
-    <t>https://www.icn.unal.edu.co</t>
-  </si>
-  <si>
-    <t>https://www.museodoria.it</t>
-  </si>
-  <si>
-    <t>https://www.vogelwarte-helgoland.de</t>
-  </si>
-  <si>
-    <t>https://www.muzeumvychodocesky.cz</t>
-  </si>
-  <si>
-    <t>https://www.biodokumentation.de</t>
-  </si>
-  <si>
-    <t>https://www.krskmuseum.ru</t>
-  </si>
-  <si>
     <t>https://www.mnhn.cl</t>
   </si>
   <si>
-    <t>https://www.coleccionphelps.org</t>
-  </si>
-  <si>
-    <t>https://www.ulasalle.ac.cr</t>
-  </si>
-  <si>
     <t>https://www.utmn.ru/en</t>
   </si>
   <si>
-    <t>https://www.uaem.mx</t>
-  </si>
-  <si>
     <t>https://www.magnt.net.au</t>
   </si>
   <si>
-    <t>https://www.fciencias.unam.mx/museosvivos</t>
-  </si>
-  <si>
     <t>https://www.ben.edu/museum</t>
-  </si>
-  <si>
-    <t>https://www.coa.edu/the-college/facilities/dorr-natural-history-museum</t>
-  </si>
-  <si>
-    <t>https://www.uwyo.edu/museum</t>
   </si>
   <si>
     <t>https://www.tbri.gov.tw/</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.nhmus.hu/en/</t>
+  </si>
+  <si>
+    <t>https://www.naturkundemuseum.uni-halle.de/</t>
+  </si>
+  <si>
+    <t>https://hamburg.leibniz-lib.de/de/</t>
+  </si>
+  <si>
+    <t>https://institutions.ville-geneve.ch/fr/mhn/</t>
+  </si>
+  <si>
+    <t>https://snm.dk/en/article/history-zoological-museum</t>
+  </si>
+  <si>
+    <t>https://www.lwl-naturkundemuseum-muenster.de/en/</t>
+  </si>
+  <si>
+    <t>https://www.zin.ru/museum/</t>
+  </si>
+  <si>
+    <t>https://www.nhm.uio.no/english/</t>
+  </si>
+  <si>
+    <t>https://brightonmuseums.org.uk/booth-museum-of-natural-history/</t>
+  </si>
+  <si>
+    <t>https://carnegiemnh.org/</t>
+  </si>
+  <si>
+    <t>https://museum.nantesmetropole.fr/home.html</t>
+  </si>
+  <si>
+    <t>https://zmmu.msu.ru/</t>
+  </si>
+  <si>
+    <t>https://naturalhistorymuseumzimbabwe.com/</t>
+  </si>
+  <si>
+    <t>https://www.heineanum.de/</t>
+  </si>
+  <si>
+    <t>https://tu-dresden.de/kustodie/sammlungen/fakultaet-umweltwissenschaften/forstzoologische-sammlung?set_language=de</t>
+  </si>
+  <si>
+    <t>https://www.zoologicalmuseum.nl/en/the-museum/</t>
+  </si>
+  <si>
+    <t>https://www.naturkundemuseum-potsdam.de/de</t>
+  </si>
+  <si>
+    <t>https://newark.osu.edu/</t>
+  </si>
+  <si>
+    <t>https://nature.ca/en/</t>
+  </si>
+  <si>
+    <t>https://www.ooekultur.at/location-detail/biodiversit%C3%A4tszentrum</t>
+  </si>
+  <si>
+    <t>https://www.mjakub.cz/?jaz=EN</t>
+  </si>
+  <si>
+    <t>https://natmuseum.ut.ee/et</t>
+  </si>
+  <si>
+    <t>https://aquazoo-duesseldorf.de/</t>
+  </si>
+  <si>
+    <t>https://www.natt.is/en</t>
+  </si>
+  <si>
+    <t>https://ornitologianeotropical.org/</t>
+  </si>
+  <si>
+    <t>https://mz.usp.br/en/</t>
+  </si>
+  <si>
+    <t>https://rbcm.ca/</t>
+  </si>
+  <si>
+    <t>https://www.musees.strasbourg.eu/</t>
+  </si>
+  <si>
+    <t>https://muzeum-przyrodnicze.uni.wroc.pl/</t>
+  </si>
+  <si>
+    <t>https://museum-neuchatel.ch/</t>
+  </si>
+  <si>
+    <t>https://www.durban.org.za/artculture/museums/natural.html</t>
+  </si>
+  <si>
+    <t>https://beatymuseum.ubc.ca/research-2/collections/cowan-tetrapod-collection/</t>
+  </si>
+  <si>
+    <t>https://collections.utu.fi/en/zoological-museum/</t>
+  </si>
+  <si>
+    <t>https://www.museum-am-schoelerberg.de/</t>
+  </si>
+  <si>
+    <t>https://noticias.uc.pt/artigos/visite-a-galeria-de-zoologia-do-museu-da-ciencia/</t>
+  </si>
+  <si>
+    <t>https://www.musees-saint-omer.fr/histoire-musee-dupuis/</t>
+  </si>
+  <si>
+    <t>https://www.pfalzmuseum.de/</t>
+  </si>
+  <si>
+    <t>https://natureum.ch/fr/</t>
+  </si>
+  <si>
+    <t>https://www.shropshiremuseums.org.uk/</t>
+  </si>
+  <si>
+    <t>https://www.mainz.de/nhm/</t>
+  </si>
+  <si>
+    <t>https://zoomuziejus.lt/</t>
+  </si>
+  <si>
+    <t>https://www.birds.org.il/en/birding-center/The-Israel-Ornithological-Center</t>
+  </si>
+  <si>
+    <t>https://www.museen-aschaffenburg.de/Naturwissenschaftliches--Museum-/DE_index_1085.html</t>
+  </si>
+  <si>
+    <t>https://www.nmz.uzh.ch/en/besucherinformation.html</t>
+  </si>
+  <si>
+    <t>https://www.fao.org/agris/es/node/124385</t>
+  </si>
+  <si>
+    <t>https://www.muzeum.rzeszow.pl/pl/</t>
+  </si>
+  <si>
+    <t>https://www.info.hazu.hr/en/jedinice/zavod-za-ornitologiju-u-zagrebu/</t>
+  </si>
+  <si>
+    <t>https://www.naturkundemuseum-erfurt.de/</t>
+  </si>
+  <si>
+    <t>https://www.crossriverheritage.org/</t>
+  </si>
+  <si>
+    <t>https://www.hetnatuurhistorisch.nl/</t>
+  </si>
+  <si>
+    <t>https://www.tshaonline.org/handbook/entries/more-robert-lee</t>
+  </si>
+  <si>
+    <t>https://moorelab.oxy.edu/</t>
+  </si>
+  <si>
+    <t>http://zoomus.lviv.ua/</t>
+  </si>
+  <si>
+    <t>https://zzps.rs/</t>
+  </si>
+  <si>
+    <t>https://msu.ru/en/</t>
+  </si>
+  <si>
+    <t>https://www.museostorianaturale.com/</t>
+  </si>
+  <si>
+    <t>https://www.uni-siegen.de/start/news/oeffentlichkeit/468692.html</t>
+  </si>
+  <si>
+    <t>https://www.museocivicodizoologia.it/it</t>
+  </si>
+  <si>
+    <t>https://www.biodivmuseum.de/de/startseite/</t>
+  </si>
+  <si>
+    <t>https://natuurmuseumfryslan.nl/?utm_source=gmb&amp;utm_medium=gmb&amp;utm_campaign=gmb&amp;utm_id=gmb&amp;utm_term=gmb&amp;utm_content=gmb</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/museugoeldi/pt-br</t>
+  </si>
+  <si>
+    <t>https://miamioh.edu/cas/centers-institutes/hefner-museum-natural-history/</t>
+  </si>
+  <si>
+    <t>https://www.storianaturale.org/carmagnola/ita/</t>
+  </si>
+  <si>
+    <t>https://www.museoameghino.gob.ar/</t>
+  </si>
+  <si>
+    <t>https://www.museoartecontemporanea.it/museo_dAumale/</t>
+  </si>
+  <si>
+    <t>https://cibet.ucr.ac.cr/museo-de-zoologia-de-la-universidad-de-costa-rica/</t>
+  </si>
+  <si>
+    <t>https://www.naturkundemuseum-bamberg.de/</t>
+  </si>
+  <si>
+    <t>https://www.isprambiente.gov.it/it</t>
+  </si>
+  <si>
+    <t>http://www.ibiologia.unam.mx/cnav/</t>
+  </si>
+  <si>
+    <t>https://www.pucrs.br/mct/</t>
+  </si>
+  <si>
+    <t>https://bpn.gov.pl/muzeum-przyrodniczo-lesne-1</t>
+  </si>
+  <si>
+    <t>https://www.naturaravenna.it/il-museo/</t>
+  </si>
+  <si>
+    <t>https://www.sema.rs.gov.br/museu-de-ciencias-naturais-mcn</t>
+  </si>
+  <si>
+    <t>https://www.museidigenova.it/it/museo-di-storia-naturale-giacomo-doria-0</t>
+  </si>
+  <si>
+    <t>https://ifv-vogelwarte.de/institut</t>
+  </si>
+  <si>
+    <t>https://museoserrano.blogspot.com/</t>
+  </si>
+  <si>
+    <t>https://ebird.org/hotspot/L2574364</t>
+  </si>
+  <si>
+    <t>https://www.muzeumhk.cz/</t>
+  </si>
+  <si>
+    <t>https://www.musee-semur-en-auxois.com/</t>
+  </si>
+  <si>
+    <t>https://www.saarland.de/mukmav/DE/portale/naturschutz/informationen/artenschutz/zentrum-fuer-biodokumentation</t>
+  </si>
+  <si>
+    <t>https://www.kkkm.ru/</t>
+  </si>
+  <si>
+    <t>網站壞掉</t>
+  </si>
+  <si>
+    <t>https://lasalle.edu.co/es/noticias/museo-de-historia-natural-de-la-salle-un-legado-cientifico-en-colombia</t>
+  </si>
+  <si>
+    <t>http://sifauna.ueuo.com/</t>
+  </si>
+  <si>
+    <t>https://pagina.fciencias.unam.mx/vida-en-ciencias/instalaciones/instalaciones-academicas/museos/museo-zoologia-colecciones</t>
+  </si>
+  <si>
+    <t>https://uwymv.wyomingbiodiversity.org/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2883,6 +2931,12 @@
       <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0563C1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2981,8 +3035,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -9579,7 +9633,9 @@
       <c r="I13">
         <v>0</v>
       </c>
-      <c r="J13" s="12"/>
+      <c r="J13" s="11" t="s">
+        <v>854</v>
+      </c>
     </row>
     <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
@@ -9611,7 +9667,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>671</v>
+        <v>855</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
@@ -9644,7 +9700,7 @@
         <v>1</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -9677,7 +9733,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -9710,7 +9766,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
@@ -9743,7 +9799,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>675</v>
+        <v>856</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -9776,10 +9832,10 @@
         <v>0</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -9809,7 +9865,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>677</v>
+        <v>858</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -9842,7 +9898,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -9875,7 +9931,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.45">
@@ -9908,7 +9964,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.45">
@@ -9941,7 +9997,7 @@
         <v>1</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -9974,7 +10030,7 @@
         <v>1</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.45">
@@ -10007,7 +10063,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -10040,10 +10096,10 @@
         <v>0</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -10072,9 +10128,7 @@
       <c r="I28">
         <v>0</v>
       </c>
-      <c r="J28" s="11" t="s">
-        <v>685</v>
-      </c>
+      <c r="J28" s="12"/>
     </row>
     <row r="29" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
@@ -10106,7 +10160,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -10139,7 +10193,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -10172,7 +10226,7 @@
         <v>1</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -10205,7 +10259,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.45">
@@ -10238,7 +10292,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -10271,7 +10325,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -10304,7 +10358,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -10337,7 +10391,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>693</v>
+        <v>859</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.45">
@@ -10370,7 +10424,7 @@
         <v>0</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>675</v>
+        <v>860</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.45">
@@ -10403,7 +10457,7 @@
         <v>0</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>694</v>
+        <v>861</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -10436,7 +10490,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.45">
@@ -10469,7 +10523,7 @@
         <v>0</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -10502,7 +10556,7 @@
         <v>0</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>697</v>
+        <v>862</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -10535,7 +10589,7 @@
         <v>1</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -10568,7 +10622,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>699</v>
+        <v>863</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -10601,7 +10655,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.45">
@@ -10634,7 +10688,7 @@
         <v>0</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -10667,10 +10721,10 @@
         <v>0</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.45">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -10700,7 +10754,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>677</v>
+        <v>858</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.45">
@@ -10733,7 +10787,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>675</v>
+        <v>865</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.45">
@@ -10766,7 +10820,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>703</v>
+        <v>694</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.45">
@@ -10799,7 +10853,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>704</v>
+        <v>695</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -10832,7 +10886,7 @@
         <v>0</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>705</v>
+        <v>866</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -10865,7 +10919,7 @@
         <v>0</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>706</v>
+        <v>696</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.45">
@@ -10898,10 +10952,10 @@
         <v>0</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="75" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>56</v>
       </c>
@@ -10930,7 +10984,9 @@
       <c r="I54">
         <v>0</v>
       </c>
-      <c r="J54" s="12"/>
+      <c r="J54" s="11" t="s">
+        <v>868</v>
+      </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
@@ -10962,7 +11018,7 @@
         <v>1</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>708</v>
+        <v>697</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.45">
@@ -10995,10 +11051,10 @@
         <v>1</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.45">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>24</v>
       </c>
@@ -11028,7 +11084,7 @@
         <v>0</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>677</v>
+        <v>858</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.45">
@@ -11061,7 +11117,7 @@
         <v>0</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.45">
@@ -11094,7 +11150,7 @@
         <v>0</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>711</v>
+        <v>700</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.45">
@@ -11127,7 +11183,7 @@
         <v>0</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>712</v>
+        <v>701</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.45">
@@ -11160,7 +11216,7 @@
         <v>0</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>713</v>
+        <v>702</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.45">
@@ -11193,7 +11249,7 @@
         <v>0</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>714</v>
+        <v>703</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -11226,7 +11282,7 @@
         <v>0</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>715</v>
+        <v>704</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -11259,7 +11315,7 @@
         <v>0</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.45">
@@ -11292,7 +11348,7 @@
         <v>0</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.45">
@@ -11325,10 +11381,10 @@
         <v>0</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.45">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>68</v>
       </c>
@@ -11358,7 +11414,7 @@
         <v>0</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>665</v>
+        <v>869</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.45">
@@ -11391,7 +11447,7 @@
         <v>0</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="60" x14ac:dyDescent="0.45">
@@ -11424,7 +11480,7 @@
         <v>0</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -11457,7 +11513,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>720</v>
+        <v>870</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -11490,7 +11546,7 @@
         <v>0</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>721</v>
+        <v>709</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -11523,7 +11579,7 @@
         <v>0</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>722</v>
+        <v>710</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -11556,7 +11612,7 @@
         <v>0</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>723</v>
+        <v>711</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -11589,7 +11645,7 @@
         <v>0</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>724</v>
+        <v>712</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -11622,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="J75" s="11" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>77</v>
       </c>
@@ -11655,7 +11711,7 @@
         <v>0</v>
       </c>
       <c r="J76" s="11" t="s">
-        <v>726</v>
+        <v>871</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -11688,7 +11744,7 @@
         <v>0</v>
       </c>
       <c r="J77" s="11" t="s">
-        <v>727</v>
+        <v>714</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -11720,7 +11776,7 @@
         <v>1</v>
       </c>
       <c r="J78" s="11" t="s">
-        <v>728</v>
+        <v>715</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -11753,7 +11809,7 @@
         <v>0</v>
       </c>
       <c r="J79" s="11" t="s">
-        <v>729</v>
+        <v>716</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.45">
@@ -11786,7 +11842,7 @@
         <v>0</v>
       </c>
       <c r="J80" s="11" t="s">
-        <v>730</v>
+        <v>717</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.45">
@@ -11819,7 +11875,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="11" t="s">
-        <v>731</v>
+        <v>872</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.45">
@@ -11883,7 +11939,7 @@
         <v>0</v>
       </c>
       <c r="J83" s="11" t="s">
-        <v>732</v>
+        <v>718</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="45" x14ac:dyDescent="0.45">
@@ -11916,10 +11972,10 @@
         <v>0</v>
       </c>
       <c r="J84" s="11" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="45" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>86</v>
       </c>
@@ -11949,7 +12005,7 @@
         <v>0</v>
       </c>
       <c r="J85" s="11" t="s">
-        <v>734</v>
+        <v>873</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.45">
@@ -11982,7 +12038,7 @@
         <v>0</v>
       </c>
       <c r="J86" s="11" t="s">
-        <v>735</v>
+        <v>720</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.45">
@@ -12015,7 +12071,7 @@
         <v>0</v>
       </c>
       <c r="J87" s="11" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.45">
@@ -12048,7 +12104,7 @@
         <v>0</v>
       </c>
       <c r="J88" s="11" t="s">
-        <v>737</v>
+        <v>722</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.45">
@@ -12081,7 +12137,7 @@
         <v>0</v>
       </c>
       <c r="J89" s="11" t="s">
-        <v>738</v>
+        <v>723</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.45">
@@ -12114,7 +12170,7 @@
         <v>0</v>
       </c>
       <c r="J90" s="11" t="s">
-        <v>739</v>
+        <v>874</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.45">
@@ -12147,7 +12203,7 @@
         <v>0</v>
       </c>
       <c r="J91" s="11" t="s">
-        <v>740</v>
+        <v>875</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -12180,7 +12236,7 @@
         <v>0</v>
       </c>
       <c r="J92" s="11" t="s">
-        <v>741</v>
+        <v>724</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -12213,7 +12269,7 @@
         <v>0</v>
       </c>
       <c r="J93" s="11" t="s">
-        <v>742</v>
+        <v>725</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="45" x14ac:dyDescent="0.45">
@@ -12246,7 +12302,7 @@
         <v>0</v>
       </c>
       <c r="J94" s="11" t="s">
-        <v>743</v>
+        <v>726</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.45">
@@ -12279,7 +12335,7 @@
         <v>0</v>
       </c>
       <c r="J95" s="11" t="s">
-        <v>744</v>
+        <v>727</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.45">
@@ -12312,7 +12368,7 @@
         <v>0</v>
       </c>
       <c r="J96" s="11" t="s">
-        <v>745</v>
+        <v>876</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -12345,7 +12401,7 @@
         <v>0</v>
       </c>
       <c r="J97" s="11" t="s">
-        <v>746</v>
+        <v>728</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -12378,7 +12434,7 @@
         <v>0</v>
       </c>
       <c r="J98" s="11" t="s">
-        <v>747</v>
+        <v>729</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -12411,10 +12467,10 @@
         <v>0</v>
       </c>
       <c r="J99" s="11" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.45">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>24</v>
       </c>
@@ -12444,7 +12500,7 @@
         <v>0</v>
       </c>
       <c r="J100" s="11" t="s">
-        <v>677</v>
+        <v>858</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.45">
@@ -12476,9 +12532,7 @@
       <c r="I101">
         <v>0</v>
       </c>
-      <c r="J101" s="11" t="s">
-        <v>749</v>
-      </c>
+      <c r="J101" s="12"/>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
@@ -12510,7 +12564,7 @@
         <v>0</v>
       </c>
       <c r="J102" s="11" t="s">
-        <v>750</v>
+        <v>730</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.45">
@@ -12543,7 +12597,7 @@
         <v>0</v>
       </c>
       <c r="J103" s="11" t="s">
-        <v>751</v>
+        <v>731</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.45">
@@ -12575,7 +12629,9 @@
       <c r="I104">
         <v>0</v>
       </c>
-      <c r="J104" s="12"/>
+      <c r="J104" s="11" t="s">
+        <v>878</v>
+      </c>
     </row>
     <row r="105" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
@@ -12607,7 +12663,7 @@
         <v>0</v>
       </c>
       <c r="J105" s="11" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.45">
@@ -12640,7 +12696,7 @@
         <v>0</v>
       </c>
       <c r="J106" s="11" t="s">
-        <v>752</v>
+        <v>879</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.45">
@@ -12673,7 +12729,7 @@
         <v>1</v>
       </c>
       <c r="J107" s="11" t="s">
-        <v>753</v>
+        <v>732</v>
       </c>
     </row>
     <row r="108" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -12706,10 +12762,10 @@
         <v>0</v>
       </c>
       <c r="J108" s="11" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>109</v>
       </c>
@@ -12738,9 +12794,7 @@
       <c r="I109">
         <v>0</v>
       </c>
-      <c r="J109" s="11" t="s">
-        <v>755</v>
-      </c>
+      <c r="J109" s="12"/>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
@@ -12772,7 +12826,7 @@
         <v>0</v>
       </c>
       <c r="J110" s="11" t="s">
-        <v>756</v>
+        <v>734</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.45">
@@ -12805,7 +12859,7 @@
         <v>0</v>
       </c>
       <c r="J111" s="11" t="s">
-        <v>757</v>
+        <v>880</v>
       </c>
     </row>
     <row r="112" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -12838,7 +12892,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="11" t="s">
-        <v>758</v>
+        <v>735</v>
       </c>
     </row>
     <row r="113" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -12870,9 +12924,7 @@
       <c r="I113">
         <v>0</v>
       </c>
-      <c r="J113" s="11" t="s">
-        <v>759</v>
-      </c>
+      <c r="J113" s="12"/>
     </row>
     <row r="114" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
@@ -12904,7 +12956,7 @@
         <v>0</v>
       </c>
       <c r="J114" s="11" t="s">
-        <v>760</v>
+        <v>736</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -12937,10 +12989,10 @@
         <v>0</v>
       </c>
       <c r="J115" s="11" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.45">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>116</v>
       </c>
@@ -12969,7 +13021,9 @@
       <c r="I116">
         <v>0</v>
       </c>
-      <c r="J116" s="12"/>
+      <c r="J116" s="11" t="s">
+        <v>882</v>
+      </c>
     </row>
     <row r="117" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
@@ -13001,7 +13055,7 @@
         <v>0</v>
       </c>
       <c r="J117" s="11" t="s">
-        <v>762</v>
+        <v>737</v>
       </c>
     </row>
     <row r="118" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -13034,7 +13088,7 @@
         <v>0</v>
       </c>
       <c r="J118" s="11" t="s">
-        <v>763</v>
+        <v>883</v>
       </c>
     </row>
     <row r="119" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -13067,7 +13121,7 @@
         <v>0</v>
       </c>
       <c r="J119" s="11" t="s">
-        <v>764</v>
+        <v>738</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.45">
@@ -13100,7 +13154,7 @@
         <v>1</v>
       </c>
       <c r="J120" s="11" t="s">
-        <v>765</v>
+        <v>739</v>
       </c>
     </row>
     <row r="121" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -13133,7 +13187,7 @@
         <v>0</v>
       </c>
       <c r="J121" s="11" t="s">
-        <v>766</v>
+        <v>884</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -13166,7 +13220,7 @@
         <v>0</v>
       </c>
       <c r="J122" s="11" t="s">
-        <v>767</v>
+        <v>740</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.45">
@@ -13199,10 +13253,10 @@
         <v>0</v>
       </c>
       <c r="J123" s="11" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" ht="45" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>124</v>
       </c>
@@ -13232,7 +13286,7 @@
         <v>0</v>
       </c>
       <c r="J124" s="11" t="s">
-        <v>769</v>
+        <v>885</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.45">
@@ -13265,7 +13319,7 @@
         <v>0</v>
       </c>
       <c r="J125" s="11" t="s">
-        <v>770</v>
+        <v>742</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.45">
@@ -13298,7 +13352,7 @@
         <v>0</v>
       </c>
       <c r="J126" s="11" t="s">
-        <v>771</v>
+        <v>743</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.45">
@@ -13331,7 +13385,7 @@
         <v>0</v>
       </c>
       <c r="J127" s="11" t="s">
-        <v>772</v>
+        <v>744</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.45">
@@ -13364,7 +13418,7 @@
         <v>0</v>
       </c>
       <c r="J128" s="11" t="s">
-        <v>773</v>
+        <v>745</v>
       </c>
     </row>
     <row r="129" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -13397,7 +13451,7 @@
         <v>0</v>
       </c>
       <c r="J129" s="11" t="s">
-        <v>774</v>
+        <v>746</v>
       </c>
     </row>
     <row r="130" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -13429,8 +13483,8 @@
       <c r="I130">
         <v>0</v>
       </c>
-      <c r="J130" s="13" t="s">
-        <v>775</v>
+      <c r="J130" s="11" t="s">
+        <v>886</v>
       </c>
     </row>
     <row r="131" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -13463,7 +13517,7 @@
         <v>0</v>
       </c>
       <c r="J131" s="11" t="s">
-        <v>776</v>
+        <v>747</v>
       </c>
     </row>
     <row r="132" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -13496,7 +13550,7 @@
         <v>1</v>
       </c>
       <c r="J132" s="11" t="s">
-        <v>777</v>
+        <v>748</v>
       </c>
     </row>
     <row r="133" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -13529,7 +13583,7 @@
         <v>0</v>
       </c>
       <c r="J133" s="11" t="s">
-        <v>778</v>
+        <v>749</v>
       </c>
     </row>
     <row r="134" spans="1:10" ht="45" x14ac:dyDescent="0.45">
@@ -13562,7 +13616,7 @@
         <v>0</v>
       </c>
       <c r="J134" s="11" t="s">
-        <v>779</v>
+        <v>750</v>
       </c>
     </row>
     <row r="135" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -13595,7 +13649,7 @@
         <v>0</v>
       </c>
       <c r="J135" s="11" t="s">
-        <v>780</v>
+        <v>751</v>
       </c>
     </row>
     <row r="136" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -13628,7 +13682,7 @@
         <v>0</v>
       </c>
       <c r="J136" s="11" t="s">
-        <v>781</v>
+        <v>752</v>
       </c>
     </row>
     <row r="137" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -13661,7 +13715,7 @@
         <v>0</v>
       </c>
       <c r="J137" s="11" t="s">
-        <v>692</v>
+        <v>756</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.45">
@@ -13694,7 +13748,7 @@
         <v>0</v>
       </c>
       <c r="J138" s="11" t="s">
-        <v>782</v>
+        <v>753</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.45">
@@ -13727,7 +13781,7 @@
         <v>0</v>
       </c>
       <c r="J139" s="11" t="s">
-        <v>783</v>
+        <v>754</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.45">
@@ -13760,7 +13814,7 @@
         <v>0</v>
       </c>
       <c r="J140" s="11" t="s">
-        <v>784</v>
+        <v>755</v>
       </c>
     </row>
     <row r="141" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -13793,7 +13847,7 @@
         <v>0</v>
       </c>
       <c r="J141" s="11" t="s">
-        <v>785</v>
+        <v>688</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.45">
@@ -13826,7 +13880,7 @@
         <v>0</v>
       </c>
       <c r="J142" s="11" t="s">
-        <v>786</v>
+        <v>757</v>
       </c>
     </row>
     <row r="143" spans="1:10" ht="45" x14ac:dyDescent="0.45">
@@ -13859,7 +13913,7 @@
         <v>0</v>
       </c>
       <c r="J143" s="11" t="s">
-        <v>787</v>
+        <v>758</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.45">
@@ -13892,7 +13946,7 @@
         <v>0</v>
       </c>
       <c r="J144" s="11" t="s">
-        <v>788</v>
+        <v>759</v>
       </c>
     </row>
     <row r="145" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -13958,7 +14012,7 @@
         <v>1</v>
       </c>
       <c r="J146" s="11" t="s">
-        <v>789</v>
+        <v>760</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.45">
@@ -13991,7 +14045,7 @@
         <v>0</v>
       </c>
       <c r="J147" s="11" t="s">
-        <v>790</v>
+        <v>761</v>
       </c>
     </row>
     <row r="148" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -14024,7 +14078,7 @@
         <v>0</v>
       </c>
       <c r="J148" s="11" t="s">
-        <v>791</v>
+        <v>887</v>
       </c>
     </row>
     <row r="149" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -14057,7 +14111,7 @@
         <v>0</v>
       </c>
       <c r="J149" s="11" t="s">
-        <v>792</v>
+        <v>762</v>
       </c>
     </row>
     <row r="150" spans="1:10" ht="45" x14ac:dyDescent="0.45">
@@ -14089,8 +14143,8 @@
       <c r="I150">
         <v>0</v>
       </c>
-      <c r="J150" s="13" t="s">
-        <v>793</v>
+      <c r="J150" s="11" t="s">
+        <v>888</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.45">
@@ -14123,7 +14177,7 @@
         <v>0</v>
       </c>
       <c r="J151" s="11" t="s">
-        <v>794</v>
+        <v>763</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.45">
@@ -14156,10 +14210,10 @@
         <v>0</v>
       </c>
       <c r="J152" s="11" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.45">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>150</v>
       </c>
@@ -14188,7 +14242,9 @@
       <c r="I153">
         <v>0</v>
       </c>
-      <c r="J153" s="12"/>
+      <c r="J153" s="11" t="s">
+        <v>889</v>
+      </c>
     </row>
     <row r="154" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
@@ -14220,7 +14276,7 @@
         <v>0</v>
       </c>
       <c r="J154" s="11" t="s">
-        <v>796</v>
+        <v>765</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.45">
@@ -14253,7 +14309,7 @@
         <v>0</v>
       </c>
       <c r="J155" s="11" t="s">
-        <v>797</v>
+        <v>766</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.45">
@@ -14286,7 +14342,7 @@
         <v>0</v>
       </c>
       <c r="J156" s="11" t="s">
-        <v>798</v>
+        <v>767</v>
       </c>
     </row>
     <row r="157" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -14319,7 +14375,7 @@
         <v>0</v>
       </c>
       <c r="J157" s="11" t="s">
-        <v>799</v>
+        <v>768</v>
       </c>
     </row>
     <row r="158" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -14352,7 +14408,7 @@
         <v>0</v>
       </c>
       <c r="J158" s="11" t="s">
-        <v>800</v>
+        <v>769</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.45">
@@ -14385,7 +14441,7 @@
         <v>0</v>
       </c>
       <c r="J159" s="11" t="s">
-        <v>801</v>
+        <v>770</v>
       </c>
     </row>
     <row r="160" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -14418,7 +14474,7 @@
         <v>0</v>
       </c>
       <c r="J160" s="11" t="s">
-        <v>802</v>
+        <v>771</v>
       </c>
     </row>
     <row r="161" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -14451,10 +14507,10 @@
         <v>0</v>
       </c>
       <c r="J161" s="11" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="162" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>159</v>
       </c>
@@ -14484,7 +14540,7 @@
         <v>0</v>
       </c>
       <c r="J162" s="11" t="s">
-        <v>804</v>
+        <v>891</v>
       </c>
     </row>
     <row r="163" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -14517,7 +14573,7 @@
         <v>0</v>
       </c>
       <c r="J163" s="11" t="s">
-        <v>805</v>
+        <v>892</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.45">
@@ -14581,10 +14637,10 @@
         <v>0</v>
       </c>
       <c r="J165" s="11" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="166" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>163</v>
       </c>
@@ -14614,7 +14670,7 @@
         <v>0</v>
       </c>
       <c r="J166" s="11" t="s">
-        <v>807</v>
+        <v>893</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.45">
@@ -14647,7 +14703,7 @@
         <v>0</v>
       </c>
       <c r="J167" s="11" t="s">
-        <v>808</v>
+        <v>773</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.45">
@@ -14680,10 +14736,10 @@
         <v>0</v>
       </c>
       <c r="J168" s="11" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.45">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" ht="45" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>166</v>
       </c>
@@ -14713,7 +14769,7 @@
         <v>0</v>
       </c>
       <c r="J169" s="11" t="s">
-        <v>810</v>
+        <v>895</v>
       </c>
     </row>
     <row r="170" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -14746,7 +14802,7 @@
         <v>0</v>
       </c>
       <c r="J170" s="11" t="s">
-        <v>811</v>
+        <v>774</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.45">
@@ -14779,10 +14835,10 @@
         <v>0</v>
       </c>
       <c r="J171" s="11" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="172" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" ht="60" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>169</v>
       </c>
@@ -14812,7 +14868,7 @@
         <v>0</v>
       </c>
       <c r="J172" s="11" t="s">
-        <v>813</v>
+        <v>896</v>
       </c>
     </row>
     <row r="173" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -14845,7 +14901,7 @@
         <v>0</v>
       </c>
       <c r="J173" s="11" t="s">
-        <v>814</v>
+        <v>776</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.45">
@@ -14878,7 +14934,7 @@
         <v>0</v>
       </c>
       <c r="J174" s="11" t="s">
-        <v>815</v>
+        <v>777</v>
       </c>
     </row>
     <row r="175" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -14911,7 +14967,7 @@
         <v>0</v>
       </c>
       <c r="J175" s="11" t="s">
-        <v>816</v>
+        <v>897</v>
       </c>
     </row>
     <row r="176" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -14944,7 +15000,7 @@
         <v>0</v>
       </c>
       <c r="J176" s="11" t="s">
-        <v>817</v>
+        <v>778</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.45">
@@ -14977,7 +15033,7 @@
         <v>0</v>
       </c>
       <c r="J177" s="11" t="s">
-        <v>818</v>
+        <v>779</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.45">
@@ -15010,7 +15066,7 @@
         <v>0</v>
       </c>
       <c r="J178" s="11" t="s">
-        <v>819</v>
+        <v>780</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.45">
@@ -15074,7 +15130,7 @@
         <v>0</v>
       </c>
       <c r="J180" s="11" t="s">
-        <v>820</v>
+        <v>781</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.45">
@@ -15107,7 +15163,7 @@
         <v>0</v>
       </c>
       <c r="J181" s="11" t="s">
-        <v>821</v>
+        <v>782</v>
       </c>
     </row>
     <row r="182" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -15140,7 +15196,7 @@
         <v>0</v>
       </c>
       <c r="J182" s="11" t="s">
-        <v>822</v>
+        <v>783</v>
       </c>
     </row>
     <row r="183" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -15173,7 +15229,7 @@
         <v>0</v>
       </c>
       <c r="J183" s="11" t="s">
-        <v>823</v>
+        <v>784</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.45">
@@ -15206,10 +15262,10 @@
         <v>0</v>
       </c>
       <c r="J184" s="11" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.45">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>182</v>
       </c>
@@ -15238,7 +15294,9 @@
       <c r="I185">
         <v>0</v>
       </c>
-      <c r="J185" s="12"/>
+      <c r="J185" s="11" t="s">
+        <v>898</v>
+      </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
@@ -15270,7 +15328,7 @@
         <v>1</v>
       </c>
       <c r="J186" s="11" t="s">
-        <v>825</v>
+        <v>786</v>
       </c>
     </row>
     <row r="187" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -15303,7 +15361,7 @@
         <v>0</v>
       </c>
       <c r="J187" s="11" t="s">
-        <v>826</v>
+        <v>787</v>
       </c>
     </row>
     <row r="188" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -15336,7 +15394,7 @@
         <v>0</v>
       </c>
       <c r="J188" s="11" t="s">
-        <v>827</v>
+        <v>788</v>
       </c>
     </row>
     <row r="189" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -15369,7 +15427,7 @@
         <v>0</v>
       </c>
       <c r="J189" s="11" t="s">
-        <v>828</v>
+        <v>789</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.45">
@@ -15402,7 +15460,7 @@
         <v>0</v>
       </c>
       <c r="J190" s="11" t="s">
-        <v>829</v>
+        <v>790</v>
       </c>
     </row>
     <row r="191" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -15435,7 +15493,7 @@
         <v>0</v>
       </c>
       <c r="J191" s="11" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
     </row>
     <row r="192" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -15468,7 +15526,7 @@
         <v>1</v>
       </c>
       <c r="J192" s="11" t="s">
-        <v>779</v>
+        <v>750</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.45">
@@ -15500,7 +15558,9 @@
       <c r="I193">
         <v>0</v>
       </c>
-      <c r="J193" s="12"/>
+      <c r="J193" s="11" t="s">
+        <v>899</v>
+      </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
@@ -15532,7 +15592,7 @@
         <v>0</v>
       </c>
       <c r="J194" s="11" t="s">
-        <v>830</v>
+        <v>791</v>
       </c>
     </row>
     <row r="195" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -15565,10 +15625,10 @@
         <v>0</v>
       </c>
       <c r="J195" s="11" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.45">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
         <v>192</v>
       </c>
@@ -15598,7 +15658,7 @@
         <v>0</v>
       </c>
       <c r="J196" s="11" t="s">
-        <v>832</v>
+        <v>901</v>
       </c>
     </row>
     <row r="197" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -15631,7 +15691,7 @@
         <v>0</v>
       </c>
       <c r="J197" s="11" t="s">
-        <v>833</v>
+        <v>792</v>
       </c>
     </row>
     <row r="198" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -15664,7 +15724,7 @@
         <v>0</v>
       </c>
       <c r="J198" s="11" t="s">
-        <v>834</v>
+        <v>793</v>
       </c>
     </row>
     <row r="199" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -15697,7 +15757,7 @@
         <v>0</v>
       </c>
       <c r="J199" s="11" t="s">
-        <v>835</v>
+        <v>794</v>
       </c>
     </row>
     <row r="200" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -15730,7 +15790,7 @@
         <v>0</v>
       </c>
       <c r="J200" s="11" t="s">
-        <v>836</v>
+        <v>795</v>
       </c>
     </row>
     <row r="201" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -15763,7 +15823,7 @@
         <v>0</v>
       </c>
       <c r="J201" s="11" t="s">
-        <v>837</v>
+        <v>796</v>
       </c>
     </row>
     <row r="202" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -15796,7 +15856,7 @@
         <v>0</v>
       </c>
       <c r="J202" s="11" t="s">
-        <v>838</v>
+        <v>797</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.45">
@@ -15828,7 +15888,9 @@
       <c r="I203">
         <v>0</v>
       </c>
-      <c r="J203" s="12"/>
+      <c r="J203" s="11" t="s">
+        <v>902</v>
+      </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
@@ -15860,7 +15922,7 @@
         <v>0</v>
       </c>
       <c r="J204" s="11" t="s">
-        <v>839</v>
+        <v>903</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.45">
@@ -15893,10 +15955,10 @@
         <v>0</v>
       </c>
       <c r="J205" s="11" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.45">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
         <v>202</v>
       </c>
@@ -15925,7 +15987,9 @@
       <c r="I206">
         <v>0</v>
       </c>
-      <c r="J206" s="12"/>
+      <c r="J206" s="11" t="s">
+        <v>904</v>
+      </c>
     </row>
     <row r="207" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
@@ -15957,7 +16021,7 @@
         <v>0</v>
       </c>
       <c r="J207" s="11" t="s">
-        <v>841</v>
+        <v>799</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.45">
@@ -15990,7 +16054,7 @@
         <v>0</v>
       </c>
       <c r="J208" s="11" t="s">
-        <v>842</v>
+        <v>800</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.45">
@@ -16023,7 +16087,7 @@
         <v>0</v>
       </c>
       <c r="J209" s="11" t="s">
-        <v>843</v>
+        <v>801</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.45">
@@ -16056,7 +16120,7 @@
         <v>0</v>
       </c>
       <c r="J210" s="11" t="s">
-        <v>844</v>
+        <v>802</v>
       </c>
     </row>
     <row r="211" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -16089,7 +16153,7 @@
         <v>#N/A</v>
       </c>
       <c r="J211" s="11" t="s">
-        <v>845</v>
+        <v>803</v>
       </c>
     </row>
     <row r="212" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -16121,8 +16185,8 @@
       <c r="I212" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J212" s="13" t="s">
-        <v>846</v>
+      <c r="J212" s="11" t="s">
+        <v>905</v>
       </c>
     </row>
     <row r="213" spans="1:10" ht="31.5" x14ac:dyDescent="0.45">
@@ -16154,7 +16218,9 @@
       <c r="I213" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J213" s="12"/>
+      <c r="J213" s="11" t="s">
+        <v>906</v>
+      </c>
     </row>
     <row r="214" spans="1:10" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A214" s="2" t="s">
@@ -16186,7 +16252,7 @@
         <v>#N/A</v>
       </c>
       <c r="J214" s="11" t="s">
-        <v>847</v>
+        <v>804</v>
       </c>
     </row>
     <row r="215" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -16219,7 +16285,7 @@
         <v>#N/A</v>
       </c>
       <c r="J215" s="11" t="s">
-        <v>848</v>
+        <v>805</v>
       </c>
     </row>
     <row r="216" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -16252,7 +16318,7 @@
         <v>#N/A</v>
       </c>
       <c r="J216" s="11" t="s">
-        <v>849</v>
+        <v>806</v>
       </c>
     </row>
     <row r="217" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -16285,7 +16351,7 @@
         <v>#N/A</v>
       </c>
       <c r="J217" s="11" t="s">
-        <v>850</v>
+        <v>807</v>
       </c>
     </row>
     <row r="218" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -16318,7 +16384,7 @@
         <v>#N/A</v>
       </c>
       <c r="J218" s="11" t="s">
-        <v>851</v>
+        <v>808</v>
       </c>
     </row>
     <row r="219" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -16351,7 +16417,7 @@
         <v>#N/A</v>
       </c>
       <c r="J219" s="11" t="s">
-        <v>852</v>
+        <v>809</v>
       </c>
     </row>
     <row r="220" spans="1:10" ht="31.5" x14ac:dyDescent="0.45">
@@ -16384,7 +16450,7 @@
         <v>#N/A</v>
       </c>
       <c r="J220" s="11" t="s">
-        <v>853</v>
+        <v>907</v>
       </c>
     </row>
     <row r="221" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -16417,7 +16483,7 @@
         <v>#N/A</v>
       </c>
       <c r="J221" s="11" t="s">
-        <v>854</v>
+        <v>810</v>
       </c>
     </row>
     <row r="222" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -16450,7 +16516,7 @@
         <v>#N/A</v>
       </c>
       <c r="J222" s="11" t="s">
-        <v>855</v>
+        <v>908</v>
       </c>
     </row>
     <row r="223" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -16483,7 +16549,7 @@
         <v>#N/A</v>
       </c>
       <c r="J223" s="11" t="s">
-        <v>856</v>
+        <v>811</v>
       </c>
     </row>
     <row r="224" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -16516,7 +16582,7 @@
         <v>#N/A</v>
       </c>
       <c r="J224" s="11" t="s">
-        <v>857</v>
+        <v>812</v>
       </c>
     </row>
     <row r="225" spans="1:10" ht="31.5" x14ac:dyDescent="0.45">
@@ -16549,7 +16615,7 @@
         <v>#N/A</v>
       </c>
       <c r="J225" s="11" t="s">
-        <v>858</v>
+        <v>813</v>
       </c>
     </row>
     <row r="226" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -16582,7 +16648,7 @@
         <v>#N/A</v>
       </c>
       <c r="J226" s="11" t="s">
-        <v>859</v>
+        <v>814</v>
       </c>
     </row>
     <row r="227" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -16615,10 +16681,10 @@
         <v>#N/A</v>
       </c>
       <c r="J227" s="11" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="228" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A228" s="2" t="s">
         <v>469</v>
       </c>
@@ -16648,7 +16714,7 @@
         <v>#N/A</v>
       </c>
       <c r="J228" s="11" t="s">
-        <v>861</v>
+        <v>909</v>
       </c>
     </row>
     <row r="229" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -16681,7 +16747,7 @@
         <v>#N/A</v>
       </c>
       <c r="J229" s="11" t="s">
-        <v>862</v>
+        <v>816</v>
       </c>
     </row>
     <row r="230" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -16714,7 +16780,7 @@
         <v>#N/A</v>
       </c>
       <c r="J230" s="11" t="s">
-        <v>863</v>
+        <v>817</v>
       </c>
     </row>
     <row r="231" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -16747,7 +16813,7 @@
         <v>#N/A</v>
       </c>
       <c r="J231" s="11" t="s">
-        <v>864</v>
+        <v>818</v>
       </c>
     </row>
     <row r="232" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -16780,7 +16846,7 @@
         <v>#N/A</v>
       </c>
       <c r="J232" s="11" t="s">
-        <v>865</v>
+        <v>819</v>
       </c>
     </row>
     <row r="233" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -16813,10 +16879,10 @@
         <v>#N/A</v>
       </c>
       <c r="J233" s="11" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="234" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10" ht="45" x14ac:dyDescent="0.45">
       <c r="A234" s="2" t="s">
         <v>475</v>
       </c>
@@ -16845,7 +16911,9 @@
       <c r="I234" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J234" s="12"/>
+      <c r="J234" s="11" t="s">
+        <v>910</v>
+      </c>
     </row>
     <row r="235" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A235" s="2" t="s">
@@ -16877,10 +16945,10 @@
         <v>#N/A</v>
       </c>
       <c r="J235" s="11" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="236" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A236" s="2" t="s">
         <v>477</v>
       </c>
@@ -16910,7 +16978,7 @@
         <v>#N/A</v>
       </c>
       <c r="J236" s="11" t="s">
-        <v>868</v>
+        <v>911</v>
       </c>
     </row>
     <row r="237" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -16943,7 +17011,7 @@
         <v>#N/A</v>
       </c>
       <c r="J237" s="11" t="s">
-        <v>869</v>
+        <v>822</v>
       </c>
     </row>
     <row r="238" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -17006,9 +17074,11 @@
       <c r="I239" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J239" s="12"/>
-    </row>
-    <row r="240" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+      <c r="J239" s="11" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10" ht="75" x14ac:dyDescent="0.45">
       <c r="A240" s="2" t="s">
         <v>481</v>
       </c>
@@ -17038,10 +17108,10 @@
         <v>#N/A</v>
       </c>
       <c r="J240" s="11" t="s">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="241" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A241" s="2" t="s">
         <v>482</v>
       </c>
@@ -17071,10 +17141,10 @@
         <v>#N/A</v>
       </c>
       <c r="J241" s="11" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="242" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" ht="45" x14ac:dyDescent="0.45">
       <c r="A242" s="2" t="s">
         <v>483</v>
       </c>
@@ -17104,10 +17174,10 @@
         <v>#N/A</v>
       </c>
       <c r="J242" s="11" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="243" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A243" s="2" t="s">
         <v>158</v>
       </c>
@@ -17137,7 +17207,7 @@
         <v>0</v>
       </c>
       <c r="J243" s="11" t="s">
-        <v>803</v>
+        <v>890</v>
       </c>
     </row>
     <row r="244" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -17170,7 +17240,7 @@
         <v>#N/A</v>
       </c>
       <c r="J244" s="11" t="s">
-        <v>873</v>
+        <v>823</v>
       </c>
     </row>
     <row r="245" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -17203,7 +17273,7 @@
         <v>#N/A</v>
       </c>
       <c r="J245" s="11" t="s">
-        <v>874</v>
+        <v>824</v>
       </c>
     </row>
     <row r="246" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -17236,7 +17306,7 @@
         <v>#N/A</v>
       </c>
       <c r="J246" s="11" t="s">
-        <v>875</v>
+        <v>825</v>
       </c>
     </row>
     <row r="247" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -17269,7 +17339,7 @@
         <v>#N/A</v>
       </c>
       <c r="J247" s="11" t="s">
-        <v>876</v>
+        <v>826</v>
       </c>
     </row>
     <row r="248" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -17302,7 +17372,7 @@
         <v>#N/A</v>
       </c>
       <c r="J248" s="11" t="s">
-        <v>877</v>
+        <v>827</v>
       </c>
     </row>
     <row r="249" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -17335,10 +17405,10 @@
         <v>#N/A</v>
       </c>
       <c r="J249" s="11" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="250" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A250" s="2" t="s">
         <v>490</v>
       </c>
@@ -17367,7 +17437,9 @@
       <c r="I250" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J250" s="12"/>
+      <c r="J250" s="11" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="251" spans="1:10" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A251" s="2" t="s">
@@ -17399,7 +17471,7 @@
         <v>#N/A</v>
       </c>
       <c r="J251" s="11" t="s">
-        <v>879</v>
+        <v>917</v>
       </c>
     </row>
     <row r="252" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -17432,7 +17504,7 @@
         <v>#N/A</v>
       </c>
       <c r="J252" s="11" t="s">
-        <v>880</v>
+        <v>829</v>
       </c>
     </row>
     <row r="253" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -17465,7 +17537,7 @@
         <v>#N/A</v>
       </c>
       <c r="J253" s="11" t="s">
-        <v>881</v>
+        <v>830</v>
       </c>
     </row>
     <row r="254" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -17498,7 +17570,7 @@
         <v>#N/A</v>
       </c>
       <c r="J254" s="11" t="s">
-        <v>882</v>
+        <v>831</v>
       </c>
     </row>
     <row r="255" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -17531,7 +17603,7 @@
         <v>#N/A</v>
       </c>
       <c r="J255" s="11" t="s">
-        <v>883</v>
+        <v>832</v>
       </c>
     </row>
     <row r="256" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -17564,7 +17636,7 @@
         <v>#N/A</v>
       </c>
       <c r="J256" s="11" t="s">
-        <v>884</v>
+        <v>833</v>
       </c>
     </row>
     <row r="257" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -17597,7 +17669,7 @@
         <v>#N/A</v>
       </c>
       <c r="J257" s="11" t="s">
-        <v>885</v>
+        <v>834</v>
       </c>
     </row>
     <row r="258" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -17663,7 +17735,7 @@
         <v>#N/A</v>
       </c>
       <c r="J259" s="11" t="s">
-        <v>886</v>
+        <v>835</v>
       </c>
     </row>
     <row r="260" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -17696,10 +17768,10 @@
         <v>#N/A</v>
       </c>
       <c r="J260" s="11" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="261" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A261" s="2" t="s">
         <v>500</v>
       </c>
@@ -17728,9 +17800,11 @@
       <c r="I261" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J261" s="12"/>
-    </row>
-    <row r="262" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+      <c r="J261" s="11" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10" ht="45" x14ac:dyDescent="0.45">
       <c r="A262" s="2" t="s">
         <v>501</v>
       </c>
@@ -17760,7 +17834,7 @@
         <v>#N/A</v>
       </c>
       <c r="J262" s="11" t="s">
-        <v>888</v>
+        <v>919</v>
       </c>
     </row>
     <row r="263" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -17793,7 +17867,7 @@
         <v>#N/A</v>
       </c>
       <c r="J263" s="11" t="s">
-        <v>889</v>
+        <v>837</v>
       </c>
     </row>
     <row r="264" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -17826,7 +17900,7 @@
         <v>#N/A</v>
       </c>
       <c r="J264" s="11" t="s">
-        <v>890</v>
+        <v>838</v>
       </c>
     </row>
     <row r="265" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -17859,7 +17933,7 @@
         <v>#N/A</v>
       </c>
       <c r="J265" s="11" t="s">
-        <v>891</v>
+        <v>839</v>
       </c>
     </row>
     <row r="266" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -17892,7 +17966,7 @@
         <v>#N/A</v>
       </c>
       <c r="J266" s="11" t="s">
-        <v>892</v>
+        <v>840</v>
       </c>
     </row>
     <row r="267" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -17925,7 +17999,7 @@
         <v>#N/A</v>
       </c>
       <c r="J267" s="11" t="s">
-        <v>893</v>
+        <v>841</v>
       </c>
     </row>
     <row r="268" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -17958,10 +18032,10 @@
         <v>#N/A</v>
       </c>
       <c r="J268" s="11" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="269" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A269" s="2" t="s">
         <v>508</v>
       </c>
@@ -17991,7 +18065,7 @@
         <v>#N/A</v>
       </c>
       <c r="J269" s="11" t="s">
-        <v>895</v>
+        <v>920</v>
       </c>
     </row>
     <row r="270" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -18024,7 +18098,7 @@
         <v>#N/A</v>
       </c>
       <c r="J270" s="11" t="s">
-        <v>896</v>
+        <v>843</v>
       </c>
     </row>
     <row r="271" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -18057,7 +18131,7 @@
         <v>#N/A</v>
       </c>
       <c r="J271" s="11" t="s">
-        <v>897</v>
+        <v>844</v>
       </c>
     </row>
     <row r="272" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -18090,7 +18164,7 @@
         <v>0</v>
       </c>
       <c r="J272" s="11" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="273" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -18123,7 +18197,7 @@
         <v>#N/A</v>
       </c>
       <c r="J273" s="11" t="s">
-        <v>898</v>
+        <v>845</v>
       </c>
     </row>
     <row r="274" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -18156,7 +18230,7 @@
         <v>#N/A</v>
       </c>
       <c r="J274" s="11" t="s">
-        <v>899</v>
+        <v>921</v>
       </c>
     </row>
     <row r="275" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -18189,7 +18263,7 @@
         <v>#N/A</v>
       </c>
       <c r="J275" s="11" t="s">
-        <v>900</v>
+        <v>922</v>
       </c>
     </row>
     <row r="276" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -18222,7 +18296,7 @@
         <v>#N/A</v>
       </c>
       <c r="J276" s="11" t="s">
-        <v>901</v>
+        <v>846</v>
       </c>
     </row>
     <row r="277" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -18255,7 +18329,7 @@
         <v>#N/A</v>
       </c>
       <c r="J277" s="11" t="s">
-        <v>902</v>
+        <v>847</v>
       </c>
     </row>
     <row r="278" spans="1:10" ht="31.5" x14ac:dyDescent="0.45">
@@ -18288,10 +18362,10 @@
         <v>#N/A</v>
       </c>
       <c r="J278" s="11" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="279" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="279" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A279" s="2" t="s">
         <v>517</v>
       </c>
@@ -18321,7 +18395,7 @@
         <v>#N/A</v>
       </c>
       <c r="J279" s="11" t="s">
-        <v>904</v>
+        <v>924</v>
       </c>
     </row>
     <row r="280" spans="1:10" ht="31.5" x14ac:dyDescent="0.45">
@@ -18353,7 +18427,9 @@
       <c r="I280" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J280" s="12"/>
+      <c r="J280" s="11" t="s">
+        <v>925</v>
+      </c>
     </row>
     <row r="281" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A281" s="2" t="s">
@@ -18385,10 +18461,10 @@
         <v>#N/A</v>
       </c>
       <c r="J281" s="11" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="282" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="282" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A282" s="2" t="s">
         <v>520</v>
       </c>
@@ -18418,7 +18494,7 @@
         <v>#N/A</v>
       </c>
       <c r="J282" s="11" t="s">
-        <v>906</v>
+        <v>926</v>
       </c>
     </row>
     <row r="283" spans="1:10" ht="31.5" x14ac:dyDescent="0.45">
@@ -18450,11 +18526,9 @@
       <c r="I283" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J283" s="11" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="284" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+      <c r="J283" s="12"/>
+    </row>
+    <row r="284" spans="1:10" ht="45" x14ac:dyDescent="0.45">
       <c r="A284" s="2" t="s">
         <v>522</v>
       </c>
@@ -18484,7 +18558,7 @@
         <v>#N/A</v>
       </c>
       <c r="J284" s="11" t="s">
-        <v>908</v>
+        <v>927</v>
       </c>
     </row>
     <row r="285" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -18548,7 +18622,7 @@
         <v>#N/A</v>
       </c>
       <c r="J286" s="11" t="s">
-        <v>909</v>
+        <v>928</v>
       </c>
     </row>
     <row r="287" spans="1:10" ht="31.5" x14ac:dyDescent="0.45">
@@ -18580,7 +18654,9 @@
       <c r="I287" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J287" s="12"/>
+      <c r="J287" s="11" t="s">
+        <v>929</v>
+      </c>
     </row>
     <row r="288" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A288" s="2" t="s">
@@ -18611,9 +18687,11 @@
       <c r="I288" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J288" s="12"/>
-    </row>
-    <row r="289" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+      <c r="J288" s="11" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="289" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A289" s="2" t="s">
         <v>527</v>
       </c>
@@ -18643,10 +18721,10 @@
         <v>#N/A</v>
       </c>
       <c r="J289" s="11" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="290" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="290" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A290" s="2" t="s">
         <v>528</v>
       </c>
@@ -18675,9 +18753,11 @@
       <c r="I290" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J290" s="12"/>
-    </row>
-    <row r="291" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+      <c r="J290" s="11" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="291" spans="1:10" ht="60" x14ac:dyDescent="0.45">
       <c r="A291" s="2" t="s">
         <v>529</v>
       </c>
@@ -18707,7 +18787,7 @@
         <v>#N/A</v>
       </c>
       <c r="J291" s="11" t="s">
-        <v>911</v>
+        <v>933</v>
       </c>
     </row>
     <row r="292" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -18740,7 +18820,7 @@
         <v>#N/A</v>
       </c>
       <c r="J292" s="11" t="s">
-        <v>912</v>
+        <v>934</v>
       </c>
     </row>
     <row r="293" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -18773,7 +18853,7 @@
         <v>#N/A</v>
       </c>
       <c r="J293" s="11" t="s">
-        <v>913</v>
+        <v>849</v>
       </c>
     </row>
     <row r="294" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -18805,11 +18885,11 @@
       <c r="I294" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J294" s="11" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="295" spans="1:10" ht="30" x14ac:dyDescent="0.45">
+      <c r="J294" s="13" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="295" spans="1:10" ht="45" x14ac:dyDescent="0.45">
       <c r="A295" s="2" t="s">
         <v>533</v>
       </c>
@@ -18839,7 +18919,7 @@
         <v>#N/A</v>
       </c>
       <c r="J295" s="11" t="s">
-        <v>915</v>
+        <v>936</v>
       </c>
     </row>
     <row r="296" spans="1:10" ht="30" x14ac:dyDescent="0.45">
@@ -18871,7 +18951,9 @@
       <c r="I296" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J296" s="12"/>
+      <c r="J296" s="11" t="s">
+        <v>937</v>
+      </c>
     </row>
     <row r="297" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A297" s="2" t="s">
@@ -18903,7 +18985,7 @@
         <v>#N/A</v>
       </c>
       <c r="J297" s="11" t="s">
-        <v>916</v>
+        <v>850</v>
       </c>
     </row>
     <row r="298" spans="1:10" ht="47.25" x14ac:dyDescent="0.45">
@@ -18935,9 +19017,7 @@
       <c r="I298" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J298" s="11" t="s">
-        <v>917</v>
-      </c>
+      <c r="J298" s="12"/>
     </row>
     <row r="299" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A299" s="2" t="s">
@@ -18969,7 +19049,7 @@
         <v>#N/A</v>
       </c>
       <c r="J299" s="11" t="s">
-        <v>918</v>
+        <v>851</v>
       </c>
     </row>
     <row r="300" spans="1:10" ht="31.5" x14ac:dyDescent="0.45">
@@ -19003,7 +19083,7 @@
       </c>
       <c r="J300" s="12"/>
     </row>
-    <row r="301" spans="1:10" ht="31.5" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:10" ht="75" x14ac:dyDescent="0.45">
       <c r="A301" s="2" t="s">
         <v>539</v>
       </c>
@@ -19033,7 +19113,7 @@
         <v>#N/A</v>
       </c>
       <c r="J301" s="11" t="s">
-        <v>919</v>
+        <v>938</v>
       </c>
     </row>
     <row r="302" spans="1:10" ht="31.5" x14ac:dyDescent="0.45">
@@ -19066,7 +19146,7 @@
         <v>#N/A</v>
       </c>
       <c r="J302" s="11" t="s">
-        <v>920</v>
+        <v>852</v>
       </c>
     </row>
     <row r="303" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -19099,10 +19179,10 @@
         <v>#N/A</v>
       </c>
       <c r="J303" s="11" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="304" spans="1:10" ht="45" x14ac:dyDescent="0.45">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="304" spans="1:10" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A304" s="4" t="s">
         <v>542</v>
       </c>
@@ -19127,9 +19207,7 @@
       <c r="I304" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J304" s="11" t="s">
-        <v>921</v>
-      </c>
+      <c r="J304" s="12"/>
     </row>
     <row r="305" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A305" s="4" t="s">
@@ -19157,10 +19235,10 @@
         <v>#N/A</v>
       </c>
       <c r="J305" s="11" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="306" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="306" spans="1:10" ht="30" x14ac:dyDescent="0.45">
       <c r="A306" s="4" t="s">
         <v>544</v>
       </c>
@@ -19186,7 +19264,7 @@
         <v>#N/A</v>
       </c>
       <c r="J306" s="11" t="s">
-        <v>922</v>
+        <v>939</v>
       </c>
     </row>
     <row r="307" spans="1:10" ht="15.75" x14ac:dyDescent="0.45">
@@ -19218,7 +19296,7 @@
         <v>1</v>
       </c>
       <c r="J307" s="11" t="s">
-        <v>923</v>
+        <v>853</v>
       </c>
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.45">
@@ -21304,289 +21382,300 @@
   <autoFilter ref="A1:I307" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="J2" r:id="rId1" display="https://www.nhm.ac.uk/" xr:uid="{305EF9E5-9F84-4710-A3B4-BAAF1B556BF1}"/>
-    <hyperlink ref="J3" r:id="rId2" display="https://wfvz.org/" xr:uid="{C3FE3725-57F4-410E-8305-5EDAF4D5D75A}"/>
-    <hyperlink ref="J4" r:id="rId3" display="https://www.zfmk.de/" xr:uid="{E70A493E-2E33-4AAB-B5CD-A86C3B3B0DFB}"/>
-    <hyperlink ref="J5" r:id="rId4" display="https://www.museumfuernaturkunde.berlin/" xr:uid="{3A8DE07C-727E-428E-97DA-774AE29969BF}"/>
-    <hyperlink ref="J6" r:id="rId5" display="https://www.nms.ac.uk/" xr:uid="{D4DB68AF-2587-408A-92ED-188E4AB2C8E5}"/>
-    <hyperlink ref="J7" r:id="rId6" display="https://www.naturalis.nl/" xr:uid="{440956A4-08C3-4723-83A0-A16798E02F8E}"/>
-    <hyperlink ref="J8" r:id="rId7" display="https://delmns.org/" xr:uid="{9DF99149-B5FA-4329-A811-910EF1769F01}"/>
-    <hyperlink ref="J9" r:id="rId8" display="https://naturalhistory.si.edu/" xr:uid="{802EF072-CCE7-4A14-A7E4-7858EB5FC0DD}"/>
-    <hyperlink ref="J10" r:id="rId9" display="https://www.luomus.fi/" xr:uid="{75C02B92-3516-48DE-84A6-18614781A22D}"/>
-    <hyperlink ref="J11" r:id="rId10" display="https://www.nrm.se/" xr:uid="{14921064-1C93-493E-9CA3-323F81DB6F8E}"/>
-    <hyperlink ref="J12" r:id="rId11" xr:uid="{B27AB6D8-8C67-48AA-8BC9-23D9C8405014}"/>
-    <hyperlink ref="J14" r:id="rId12" display="https://www.naturwissenschaften.uni-halle.de/" xr:uid="{86EFB77F-F4BF-487F-A2B6-045DC8679C11}"/>
-    <hyperlink ref="J15" r:id="rId13" display="https://www.fieldmuseum.org/" xr:uid="{D656EF1B-2817-43D6-9979-FCBB0E996A04}"/>
-    <hyperlink ref="J16" r:id="rId14" display="https://www.australianmuseum.net.au/" xr:uid="{8DD7AFA7-369B-4CAA-B35E-52FA55801D18}"/>
-    <hyperlink ref="J17" r:id="rId15" display="https://www.3landesmuseen.de/" xr:uid="{8BD06430-411D-47D0-A0A9-4F28A83D8EE6}"/>
-    <hyperlink ref="J18" r:id="rId16" display="https://www.zin.ru/" xr:uid="{294FCC86-4C84-4153-9663-8FF2EF47AAFD}"/>
-    <hyperlink ref="J19" r:id="rId17" xr:uid="{677FA51E-44D3-4B17-8748-21A95A12DAA1}"/>
-    <hyperlink ref="J20" r:id="rId18" display="https://snm.ku.dk/" xr:uid="{5EF57A96-8465-48E0-A7B1-A88C45856049}"/>
-    <hyperlink ref="J21" r:id="rId19" display="https://www.amnh.org/" xr:uid="{48F4C0AF-F95F-490E-A420-A82E4DFB506D}"/>
-    <hyperlink ref="J22" r:id="rId20" display="https://www.senckenberg.de/" xr:uid="{F711B65E-E4A1-43F0-BA93-81F1B7C8DC40}"/>
-    <hyperlink ref="J23" r:id="rId21" display="https://www.royalalbertamuseum.ca/" xr:uid="{A606B635-1FE0-4CE3-B166-E58CDE6C9FC0}"/>
-    <hyperlink ref="J24" r:id="rId22" display="https://mvz.berkeley.edu/" xr:uid="{3176FFE3-55A4-4721-A026-8AE9F9E0348C}"/>
-    <hyperlink ref="J25" r:id="rId23" display="https://peabody.yale.edu/" xr:uid="{D9559ABB-0E7F-44A7-A47C-CBE43C3ACF37}"/>
-    <hyperlink ref="J26" r:id="rId24" display="https://www.nhm-wien.ac.at/" xr:uid="{730D40B5-FF5C-4BF5-8A14-9DC5E90F4F38}"/>
-    <hyperlink ref="J27" r:id="rId25" xr:uid="{48A054E3-1374-4D69-B87D-DA8093671CA9}"/>
-    <hyperlink ref="J28" r:id="rId26" xr:uid="{B04BA99C-C06D-4F35-ACFC-1A81C3498BDF}"/>
-    <hyperlink ref="J29" r:id="rId27" display="https://www.uwgb.edu/" xr:uid="{7F7F0DB7-FDC9-4A4E-9DD3-377AF62ADD55}"/>
-    <hyperlink ref="J30" r:id="rId28" display="https://www.landesmuseum-hannover.de/" xr:uid="{A35A0D2A-8A33-4913-9293-9E9441E2CC5A}"/>
-    <hyperlink ref="J31" r:id="rId29" display="https://mcz.harvard.edu/" xr:uid="{8845D1A9-9C16-4AB9-8726-18FB3712D0E0}"/>
-    <hyperlink ref="J32" r:id="rId30" display="https://www.museum.manchester.ac.uk/" xr:uid="{C0C5879C-D273-4D3B-B142-D28C97E418B1}"/>
-    <hyperlink ref="J33" r:id="rId31" display="https://www.rom.on.ca/" xr:uid="{52C0D326-D156-4E9A-92B9-182DACE2F686}"/>
-    <hyperlink ref="J34" r:id="rId32" display="https://www.floridamuseum.ufl.edu/" xr:uid="{63397106-1FC0-469D-A2B2-62B735FBC660}"/>
-    <hyperlink ref="J35" r:id="rId33" display="https://www.naturkundemuseum-bw.de/" xr:uid="{F2DDF4B4-FF51-4395-8678-93967FCFEDB7}"/>
-    <hyperlink ref="J36" r:id="rId34" display="https://www.lwl-naturkundemuseum.de/" xr:uid="{501186FE-D0A3-4A56-87FD-BA6C00871503}"/>
-    <hyperlink ref="J37" r:id="rId35" display="https://www.zin.ru/" xr:uid="{58B5E02A-1E5F-405E-B099-B977BA1BCCEF}"/>
-    <hyperlink ref="J38" r:id="rId36" display="https://www.nhm.uio.no/" xr:uid="{53DF4A6B-5F99-4CC1-8872-466C2A0DD8D5}"/>
-    <hyperlink ref="J39" r:id="rId37" xr:uid="{FAE3D550-9C0F-4E91-BBCC-A6751F17AA9F}"/>
-    <hyperlink ref="J40" r:id="rId38" display="https://greatnorthmuseum.org.uk/" xr:uid="{1464C8EF-0A20-4AA5-8D4F-77D0CBB7F543}"/>
-    <hyperlink ref="J41" r:id="rId39" xr:uid="{0BC98641-79C7-4833-B648-C34B57B87F81}"/>
-    <hyperlink ref="J42" r:id="rId40" display="https://www.sbnature.org/" xr:uid="{506108A7-C6EE-460A-A4D6-B3DF6F834E9D}"/>
-    <hyperlink ref="J43" r:id="rId41" xr:uid="{8AF84715-CDE6-4B68-8C33-B4A82E9AFFEF}"/>
-    <hyperlink ref="J44" r:id="rId42" display="https://www.ditsong.org.za/" xr:uid="{9BEE9812-176C-4ADD-9924-1D1D75DDF350}"/>
-    <hyperlink ref="J45" r:id="rId43" display="https://www.nmbe.ch/" xr:uid="{69827152-2C68-4637-9BF0-8E08D340BF3D}"/>
-    <hyperlink ref="J46" r:id="rId44" display="https://museum.nantes.fr/" xr:uid="{C2AE445D-DC27-48F6-A687-E9B15E61A556}"/>
-    <hyperlink ref="J47" r:id="rId45" display="https://snm.ku.dk/" xr:uid="{FEE908DB-05A4-4879-8A1E-8AFDD5AEDB31}"/>
-    <hyperlink ref="J48" r:id="rId46" display="https://www.zin.ru/" xr:uid="{5A59B7BA-E9B7-4B0E-A0A7-DFAFF2426248}"/>
-    <hyperlink ref="J49" r:id="rId47" display="https://museum.wales/" xr:uid="{7E82B024-5C8B-490D-AE51-BE9CD9A305E2}"/>
-    <hyperlink ref="J50" r:id="rId48" display="https://www.museum.zoo.cam.ac.uk/" xr:uid="{AA16513B-BE3A-4971-872D-19D0B79C5EED}"/>
-    <hyperlink ref="J51" r:id="rId49" display="https://www.nhmbulawayo.ac.zw/" xr:uid="{5B38448B-3E17-48A2-B070-BE244ABBA6BD}"/>
-    <hyperlink ref="J52" r:id="rId50" display="https://www.calacademy.org/" xr:uid="{A2AD621E-F7C3-4970-9231-9388D67BF1C1}"/>
-    <hyperlink ref="J53" r:id="rId51" display="https://www.museumheineanum.de/" xr:uid="{054B98F8-FAE3-471E-9F3F-F0AA87BC7CEB}"/>
-    <hyperlink ref="J55" r:id="rId52" display="https://www.samuseum.sa.gov.au/" xr:uid="{41A2A77C-AA7B-4181-829B-2D6FB2D3CD64}"/>
-    <hyperlink ref="J56" r:id="rId53" display="https://museumsvictoria.com.au/" xr:uid="{E762C062-32FA-4868-AE85-590E6D3894D3}"/>
-    <hyperlink ref="J57" r:id="rId54" display="https://snm.ku.dk/" xr:uid="{15BBA4B0-706B-423B-BD52-47820E71BCD4}"/>
-    <hyperlink ref="J58" r:id="rId55" display="https://www.umass.edu/" xr:uid="{DC83589E-DFFF-431E-BE76-2F16F6CD0FB6}"/>
-    <hyperlink ref="J59" r:id="rId56" display="https://www.meeresmuseum.de/" xr:uid="{A99A4A6E-B93A-4CE4-8D38-1DD3A7E74109}"/>
-    <hyperlink ref="J60" r:id="rId57" display="https://www.nysm.nysed.gov/" xr:uid="{26C2D69E-A53F-4F1F-982F-7A126566A82F}"/>
-    <hyperlink ref="J61" r:id="rId58" display="https://www.boltonlams.co.uk/" xr:uid="{B3F72B13-8983-4674-9AAF-866385E42D93}"/>
-    <hyperlink ref="J62" r:id="rId59" display="https://www.clemson.edu/" xr:uid="{72261BFE-896B-442D-9CE4-F1DEE311CD6B}"/>
-    <hyperlink ref="J63" r:id="rId60" display="https://www.naturkundemuseum.leipzig.de/" xr:uid="{54C713B2-49B4-4761-8FA9-BB39CA293A6A}"/>
-    <hyperlink ref="J64" r:id="rId61" display="https://www.senckenberg.de/" xr:uid="{3410C872-6D0D-4EE5-A1DD-DB9EE69A0D13}"/>
-    <hyperlink ref="J65" r:id="rId62" display="https://www.nm.cz/" xr:uid="{77579782-3864-43C1-8921-E8C0C9DC6979}"/>
-    <hyperlink ref="J66" r:id="rId63" display="https://www.mnhn.fr/" xr:uid="{5B143BE9-3AC1-459E-B255-19806739FACD}"/>
-    <hyperlink ref="J67" r:id="rId64" display="https://www.naturalis.nl/" xr:uid="{C2F1AA52-6C45-4920-AF8D-A350764F0AC8}"/>
-    <hyperlink ref="J68" r:id="rId65" display="https://www.readingmuseum.org.uk/" xr:uid="{7793CA43-F4A9-4C62-B3AB-01CCD05885D0}"/>
-    <hyperlink ref="J69" r:id="rId66" xr:uid="{1025AA57-1B5B-404C-B5D6-0AD62FB47B3C}"/>
-    <hyperlink ref="J70" r:id="rId67" display="https://www.naturkundemuseum.potsdam.de/" xr:uid="{A16EF87F-CBB2-4992-95C2-42C104069933}"/>
-    <hyperlink ref="J71" r:id="rId68" display="https://www.burkemuseum.org/" xr:uid="{5F3BE00E-72A6-4D4A-9658-569383A8F209}"/>
-    <hyperlink ref="J72" r:id="rId69" display="https://www.humboldt.org.co/" xr:uid="{9A42798F-6B92-4D60-9A47-43925581813B}"/>
-    <hyperlink ref="J73" r:id="rId70" xr:uid="{E43AF25A-07EB-4799-A7D1-536EFFAAD764}"/>
-    <hyperlink ref="J74" r:id="rId71" display="https://www.nhm-rudolstadt.de/" xr:uid="{B8A1C78A-F091-4D40-BFE5-9E1938DACDF5}"/>
-    <hyperlink ref="J75" r:id="rId72" display="https://www.illinoisstatemuseum.org/" xr:uid="{E6F6B6E0-2917-4E40-B753-D2B9A0443CC7}"/>
-    <hyperlink ref="J76" r:id="rId73" xr:uid="{E4AF8ECD-62AE-4656-B67C-61266D5C0515}"/>
-    <hyperlink ref="J77" r:id="rId74" display="https://www.dmns.org/" xr:uid="{314605CA-9F0F-40FC-9ED6-0B777D7B4494}"/>
-    <hyperlink ref="J78" r:id="rId75" xr:uid="{C77503B3-D3F3-4A93-9FF7-58B3BC5B168D}"/>
-    <hyperlink ref="J79" r:id="rId76" xr:uid="{63846C4E-30C1-4B4D-A124-C6D04A1537FD}"/>
-    <hyperlink ref="J80" r:id="rId77" display="https://www.mueritzeum.de/" xr:uid="{8A81ECBD-94B6-453F-9DC0-9A55A5B112D9}"/>
-    <hyperlink ref="J81" r:id="rId78" display="https://www.nature.ca/" xr:uid="{17D9B446-5280-41C6-ADF4-23611A35E649}"/>
-    <hyperlink ref="J83" r:id="rId79" display="https://www.charlestonmuseum.org/" xr:uid="{0C2196BF-A023-4416-9D2B-A49361DD6CBE}"/>
-    <hyperlink ref="J84" r:id="rId80" display="https://samnoblemuseum.ou.edu/" xr:uid="{95EE65BE-0D72-4AED-B931-353FD85E8EAC}"/>
-    <hyperlink ref="J85" r:id="rId81" display="https://www.biologiezentrum.at/" xr:uid="{E3C1F6E9-05E6-4503-AE03-261BF668E361}"/>
-    <hyperlink ref="J86" r:id="rId82" display="https://www.tulliehouse.co.uk/" xr:uid="{A48F0356-91FE-4EA7-A8C0-6E4322D825B3}"/>
-    <hyperlink ref="J87" r:id="rId83" display="https://www.welderwildlife.org/" xr:uid="{B99EB115-CAFD-4F9C-B9B9-D7651B8C664F}"/>
-    <hyperlink ref="J88" r:id="rId84" display="https://www.uebersee-museum.de/" xr:uid="{73FD2704-FD43-4138-AFB7-966B4F6224D5}"/>
-    <hyperlink ref="J89" r:id="rId85" display="https://www.theherbert.org/" xr:uid="{267C1299-5B7D-4C30-A253-739AFB2E92BB}"/>
-    <hyperlink ref="J90" r:id="rId86" display="https://www.muzeumkomensky.cz/" xr:uid="{73964F04-40E8-4C34-98B4-0895AAB1548E}"/>
-    <hyperlink ref="J91" r:id="rId87" display="https://loodusmuuseum.ee/" xr:uid="{1A5C83F1-D7B4-43F2-8DF8-6BC2BABEC79F}"/>
-    <hyperlink ref="J92" r:id="rId88" display="https://www.naturkunde-museum-coburg.de/" xr:uid="{D14EC4DA-0BAA-4D25-899E-D5270A0DE636}"/>
-    <hyperlink ref="J93" r:id="rId89" display="https://museumsandgalleries.leeds.gov.uk/" xr:uid="{7C7A27E5-023A-431E-9986-F7E173F388FF}"/>
-    <hyperlink ref="J94" r:id="rId90" display="https://www.isez.pan.krakow.pl/" xr:uid="{B5CB0808-F0DF-44BB-B5F3-2C23619434B1}"/>
-    <hyperlink ref="J95" r:id="rId91" display="https://www.tulsazoo.org/" xr:uid="{758FF71D-BBAA-4B4C-9E67-9E456D235989}"/>
-    <hyperlink ref="J96" r:id="rId92" display="https://www.aquazoo.de/" xr:uid="{B237643D-A3C3-4F0B-96AC-447AE4C04A82}"/>
-    <hyperlink ref="J97" r:id="rId93" xr:uid="{466FCBE8-A3DA-43DB-88EA-BB3D938CC242}"/>
-    <hyperlink ref="J98" r:id="rId94" display="https://www.naturundmensch.de/" xr:uid="{15E091AD-A494-4547-A06A-145BA2D46297}"/>
-    <hyperlink ref="J99" r:id="rId95" display="https://www.ni.is/" xr:uid="{F37C140B-18AA-40D6-BE1B-8FBEE3B178D2}"/>
-    <hyperlink ref="J100" r:id="rId96" display="https://snm.ku.dk/" xr:uid="{1B546185-3DA6-48D8-A764-6DEE6E980023}"/>
-    <hyperlink ref="J101" r:id="rId97" display="https://www.msn.univr.it/" xr:uid="{02E88248-3553-4E4D-B59E-1AE6782F7EF5}"/>
-    <hyperlink ref="J102" r:id="rId98" display="https://mlbean.byu.edu/" xr:uid="{E3603CA5-6C2F-4430-91F7-7BC4D776F8F3}"/>
-    <hyperlink ref="J103" r:id="rId99" display="https://www.bristolmuseums.org.uk/" xr:uid="{B270E02B-0BE9-422C-8E30-F0496135B3E6}"/>
-    <hyperlink ref="J105" r:id="rId100" display="https://www.senckenberg.de/" xr:uid="{7C0A0E8F-30DE-4620-AA64-6A9212A1C3EF}"/>
-    <hyperlink ref="J106" r:id="rId101" display="https://www.mz.usp.br/" xr:uid="{EEE6CEA5-045A-49DB-A306-3C38BF1C31BA}"/>
-    <hyperlink ref="J107" r:id="rId102" display="https://www.unr.edu/" xr:uid="{7D3CEFB7-8BBA-45C5-BE1C-D8234F323A86}"/>
-    <hyperlink ref="J108" r:id="rId103" display="https://www.saffronwaldenmuseum.org/" xr:uid="{0162D4FB-7182-4BDB-A6A4-B1EBDD50EEDD}"/>
-    <hyperlink ref="J109" r:id="rId104" xr:uid="{BF9202AF-7E92-4781-9B6D-2DB40A507D19}"/>
-    <hyperlink ref="J110" r:id="rId105" display="https://www.mpm.edu/" xr:uid="{7076F7A3-49D6-4A36-87A3-2C8CD19B02FD}"/>
-    <hyperlink ref="J111" r:id="rId106" display="https://royalbcmuseum.bc.ca/" xr:uid="{F6746C90-C801-4DF0-9F3E-1DFC53C995EE}"/>
-    <hyperlink ref="J112" r:id="rId107" display="https://www.vt.edu/" xr:uid="{E542BCD3-65E1-4D9C-BF42-247DDAB92088}"/>
-    <hyperlink ref="J113" r:id="rId108" display="https://www.annistonmuseum.org/" xr:uid="{17C92811-336E-48E3-AD9F-6DAB480C0B7D}"/>
-    <hyperlink ref="J114" r:id="rId109" display="https://www.cmnh.org/" xr:uid="{3A520C00-346F-4B50-85EB-BE17F7B523BB}"/>
-    <hyperlink ref="J115" r:id="rId110" xr:uid="{F2A2E048-05BF-403D-97D7-650AFD78CDCF}"/>
-    <hyperlink ref="J117" r:id="rId111" display="https://www.oumnh.ox.ac.uk/" xr:uid="{34D74B05-E260-4DC8-915B-4656D9580E3D}"/>
-    <hyperlink ref="J118" r:id="rId112" xr:uid="{E514B070-6260-49DE-A700-58071E0B19D9}"/>
-    <hyperlink ref="J119" r:id="rId113" display="https://biodiversity.ku.edu/" xr:uid="{739A3440-6252-4C45-A645-3D1438E24D43}"/>
-    <hyperlink ref="J120" r:id="rId114" display="https://www.birds.cornell.edu/" xr:uid="{595C7589-909F-481E-905B-2F85D861B6B7}"/>
-    <hyperlink ref="J121" r:id="rId115" display="https://www.durbannaturalsciencemuseum.org.za/" xr:uid="{BF588EA0-5A50-4938-8BDA-F023B9BA1ACE}"/>
-    <hyperlink ref="J122" r:id="rId116" display="https://www.museum.toulouse.fr/" xr:uid="{A8568CC8-6F5A-4028-AC8E-72D0A828AE98}"/>
-    <hyperlink ref="J123" r:id="rId117" display="https://www.museum.qld.gov.au/" xr:uid="{3AEBEB0F-16F3-4F6B-A9EC-DCF9126DDDC4}"/>
-    <hyperlink ref="J124" r:id="rId118" xr:uid="{D1D2B255-E4E5-4F91-A4E3-065967086BB7}"/>
-    <hyperlink ref="J125" r:id="rId119" xr:uid="{FD037215-C041-4F94-A145-B1B27E13604A}"/>
-    <hyperlink ref="J126" r:id="rId120" display="https://www.uark.edu/" xr:uid="{927BD74B-325A-4957-86F2-433A0BB307DE}"/>
-    <hyperlink ref="J127" r:id="rId121" display="https://www.museum.wa.gov.au/" xr:uid="{CB403132-1A3A-47BF-9D8E-E57B90EA25B6}"/>
-    <hyperlink ref="J128" r:id="rId122" display="https://www.sciencemuseum.org.uk/" xr:uid="{3272CFD5-DC8F-4462-8D86-E519AFE9CF8F}"/>
-    <hyperlink ref="J129" r:id="rId123" display="https://www.africamuseum.be/" xr:uid="{7325B434-5D99-4A6D-9394-9242C9B21988}"/>
-    <hyperlink ref="J130" r:id="rId124" xr:uid="{74D8436C-4364-4718-A134-71ABCAE746BC}"/>
-    <hyperlink ref="J131" r:id="rId125" display="https://www.rammuseum.org.uk/" xr:uid="{545FA4E9-FB9C-4195-A8C4-BD673EADDE68}"/>
-    <hyperlink ref="J132" r:id="rId126" display="https://cumuseum.colorado.edu/" xr:uid="{5D553146-6F0D-4745-B1C2-95F03A647CF4}"/>
-    <hyperlink ref="J133" r:id="rId127" display="https://www.tau.ac.il/" xr:uid="{4C5A4E01-9CE2-449C-A803-349262AC5249}"/>
-    <hyperlink ref="J134" r:id="rId128" display="https://www.bellmuseum.umn.edu/" xr:uid="{BC6E951B-E517-4C70-8BD7-96309CB68D4A}"/>
-    <hyperlink ref="J135" r:id="rId129" display="https://www.zemaljskimuzej.ba/" xr:uid="{A61B3D8D-1AA3-42C3-B304-2283CF5BAF7B}"/>
-    <hyperlink ref="J136" r:id="rId130" display="https://www.museum.unl.edu/" xr:uid="{DA60BF36-A212-4D47-B6D1-0CA313A2CE0D}"/>
-    <hyperlink ref="J137" r:id="rId131" display="https://www.naturkundemuseum-bw.de/" xr:uid="{DCA214C1-12ED-4C58-AD0F-6B0157AE34E0}"/>
-    <hyperlink ref="J138" r:id="rId132" display="https://www.ebd.csic.es/" xr:uid="{CF1CE84A-E902-4E86-8CC4-8DFB725971B3}"/>
-    <hyperlink ref="J139" r:id="rId133" display="https://www.muzeum.bytom.pl/" xr:uid="{0B154DEF-0F88-4369-A7CD-0257E3200C8A}"/>
-    <hyperlink ref="J140" r:id="rId134" display="https://www.otagomuseum.nz/" xr:uid="{87E0E236-4EAF-4925-8657-1FDF0A2DBFE3}"/>
-    <hyperlink ref="J141" r:id="rId135" display="https://www.museumfuernaturkunde.berlin/" xr:uid="{75A33638-2F2B-446B-9112-5CFC70D552CE}"/>
-    <hyperlink ref="J142" r:id="rId136" display="https://www.museum-westlausitz.de/" xr:uid="{E7EBFA8F-35CC-4F5B-9808-B5ACF291D27E}"/>
-    <hyperlink ref="J143" r:id="rId137" display="https://www.antipa.ro/" xr:uid="{4346C0A4-F134-4EE9-BB4C-E5F659DFB6D4}"/>
-    <hyperlink ref="J144" r:id="rId138" display="https://www.vsmuzeum.sk/" xr:uid="{FDCE2AC6-7AC7-4D48-9569-1A8B07640DC7}"/>
-    <hyperlink ref="J145" r:id="rId139" display="https://naturalhistory.si.edu/" xr:uid="{4BB9C780-46E6-45B4-844B-79EE0E1BBD58}"/>
-    <hyperlink ref="J146" r:id="rId140" display="https://www.naturemuseum.org/" xr:uid="{F9792349-402D-4845-8C88-5ED69930EDD0}"/>
-    <hyperlink ref="J147" r:id="rId141" display="https://www.aucklandmuseum.com/" xr:uid="{070F7A21-0EF8-4EC3-853F-45AB25430A0C}"/>
-    <hyperlink ref="J148" r:id="rId142" display="https://www.museumamschoelerberg.de/" xr:uid="{F9C16758-B4F5-4072-A34A-CA7DE7A2D6FF}"/>
-    <hyperlink ref="J149" r:id="rId143" display="https://www.ccmuseum.com/" xr:uid="{0EE4FED8-34B9-43F7-9FF1-0BD56A7F04B7}"/>
-    <hyperlink ref="J150" r:id="rId144" xr:uid="{2D7443E0-CA0C-4037-BAFA-A281382564B2}"/>
-    <hyperlink ref="J151" r:id="rId145" display="https://www.tepapa.govt.nz/" xr:uid="{6845CA5C-3A4E-49B9-95AE-DEC0F1EDB117}"/>
-    <hyperlink ref="J152" r:id="rId146" display="https://www.museum-wiesbaden.de/" xr:uid="{B9E72A22-042B-4FA6-90D8-40B60C30F14A}"/>
-    <hyperlink ref="J154" r:id="rId147" display="https://www.macnconicet.gob.ar/" xr:uid="{0F368DFC-2017-4D88-B89D-545EBC9514C2}"/>
-    <hyperlink ref="J155" r:id="rId148" display="https://www.museunacional.ufrj.br/" xr:uid="{A7ACECEF-D9E3-4EEE-BAE8-C994E45D24B2}"/>
-    <hyperlink ref="J156" r:id="rId149" display="https://www.darwinmuseum.ru/" xr:uid="{83120F89-EAE9-41B1-B10C-249FD136DCFE}"/>
-    <hyperlink ref="J157" r:id="rId150" display="https://www.birminghammuseums.org.uk/" xr:uid="{A46CE3E7-37CC-4195-A921-412A3BADAD07}"/>
-    <hyperlink ref="J158" r:id="rId151" display="https://mnh.uiowa.edu/" xr:uid="{8DBD39F9-847A-42FD-B68A-0A1C1D47424F}"/>
-    <hyperlink ref="J159" r:id="rId152" display="https://www.fairbanksmuseum.org/" xr:uid="{C61491C7-B2CD-4D1F-9828-7B35E3406007}"/>
-    <hyperlink ref="J160" r:id="rId153" display="https://mnch.uoregon.edu/" xr:uid="{F65197EC-6209-4C46-A597-32C4C04A8FC5}"/>
-    <hyperlink ref="J161" r:id="rId154" xr:uid="{F10C25E1-7184-44D0-8D09-ABB2844B0B09}"/>
-    <hyperlink ref="J162" r:id="rId155" xr:uid="{A6304F18-9F15-4CF7-B6E0-987053C87438}"/>
-    <hyperlink ref="J163" r:id="rId156" display="https://www.shropshiremuseums.co.uk/" xr:uid="{45FF360E-11F5-473A-97C6-C4C2ED758CC7}"/>
-    <hyperlink ref="J165" r:id="rId157" display="https://www.arizona.edu/" xr:uid="{F64E4644-ECE1-418D-9FC6-30459D6DCA45}"/>
-    <hyperlink ref="J166" r:id="rId158" display="https://www.landesmuseum-mainz.de/" xr:uid="{23837F34-9CF6-429A-97FA-D40028E96033}"/>
-    <hyperlink ref="J167" r:id="rId159" display="https://www.mos.org/" xr:uid="{CB57DD27-2A84-458E-A765-7041E1236E6E}"/>
-    <hyperlink ref="J168" r:id="rId160" display="https://gamtostyrimai.vdu.lt/" xr:uid="{6D935B87-1B93-4A9C-B613-60643144798C}"/>
-    <hyperlink ref="J169" r:id="rId161" display="https://steinhardt.museum.tau.ac.il/" xr:uid="{61EEFEA6-E311-4CC2-BFE3-B21BE40AD475}"/>
-    <hyperlink ref="J170" r:id="rId162" display="https://www.qvmag.tas.gov.au/" xr:uid="{2972802B-51DE-441F-A4F6-CDA01E793EB9}"/>
-    <hyperlink ref="J171" r:id="rId163" display="https://www.zsm.mwn.de/" xr:uid="{E51501C3-5F73-4B44-9A7F-26E12EEC98F1}"/>
-    <hyperlink ref="J172" r:id="rId164" display="https://museum.aschaffenburg.de/" xr:uid="{2AB40949-9E34-4C2E-8D42-E0F4E4B7B8D4}"/>
-    <hyperlink ref="J173" r:id="rId165" display="https://www.lillo.org.ar/" xr:uid="{46E3F80E-0046-4D25-B6AB-E79799D6EE79}"/>
-    <hyperlink ref="J174" r:id="rId166" display="https://www.muzeumbardejov.sk/" xr:uid="{3E9D0A6F-95B3-489B-A03D-F43F43CA8A6C}"/>
-    <hyperlink ref="J175" r:id="rId167" display="https://www.zoologicalmuseum.uzh.ch/" xr:uid="{4D25515A-6F19-499B-B5E8-E3B7EEC756C4}"/>
-    <hyperlink ref="J176" r:id="rId168" display="https://biodiversity.uconn.edu/" xr:uid="{FBCAC932-E778-488B-A7B1-850458EB1DFD}"/>
-    <hyperlink ref="J177" r:id="rId169" display="https://www.wisc.edu/" xr:uid="{1F7243BB-04C7-43F7-BD65-DC90772A1916}"/>
-    <hyperlink ref="J178" r:id="rId170" display="https://www.usask.ca/" xr:uid="{31007053-4BD2-4CD8-9D21-8883782987F0}"/>
-    <hyperlink ref="J180" r:id="rId171" display="https://inhs.illinois.edu/" xr:uid="{9E7B0487-4543-4373-AA1E-F1572115A2A6}"/>
-    <hyperlink ref="J181" r:id="rId172" display="https://www.unm.edu/" xr:uid="{8D0E3D3D-F0A3-40CA-AB97-D7F19928B705}"/>
-    <hyperlink ref="J182" r:id="rId173" display="https://www.museedesconfluences.fr/" xr:uid="{8F549B42-2E6D-4E62-99EF-D112E37FF65E}"/>
-    <hyperlink ref="J183" r:id="rId174" display="https://statemuseumpa.org/" xr:uid="{6787E550-77FF-4EBC-885D-8B31EC2979F5}"/>
-    <hyperlink ref="J184" r:id="rId175" display="https://www.sewanee.edu/" xr:uid="{F252E0D3-2441-4A87-951E-92CE3E767363}"/>
-    <hyperlink ref="J186" r:id="rId176" display="https://www.humboldt.edu/" xr:uid="{DBAE2BDC-0ACC-4FAD-B268-D1EBE627D4FB}"/>
-    <hyperlink ref="J187" r:id="rId177" xr:uid="{8F289792-4A61-4F92-9C0F-30ECD4E1CD24}"/>
-    <hyperlink ref="J188" r:id="rId178" display="https://www.phyletisches-museum.uni-jena.de/" xr:uid="{65473FB1-BEAE-4EE9-B3A4-62964D013440}"/>
-    <hyperlink ref="J189" r:id="rId179" display="https://www.yorkshiremuseum.org.uk/" xr:uid="{8B96CAB1-847B-4C18-A415-1D6F27D69832}"/>
-    <hyperlink ref="J190" r:id="rId180" display="https://www.sciencebuff.org/" xr:uid="{8AFEBEBD-CF76-4AE4-98E1-6A71D038E9A0}"/>
-    <hyperlink ref="J191" r:id="rId181" display="https://www.naturkundemuseum-bw.de/" xr:uid="{B0050FBD-30BC-47B2-BC2A-180573F3EC81}"/>
-    <hyperlink ref="J192" r:id="rId182" display="https://www.bellmuseum.umn.edu/" xr:uid="{5916B8D1-CB43-492C-98F8-6D306E09C509}"/>
-    <hyperlink ref="J194" r:id="rId183" display="https://www.adams.edu/" xr:uid="{552480C7-EB6E-4CBF-A193-901242CF1556}"/>
-    <hyperlink ref="J195" r:id="rId184" xr:uid="{2473D958-5685-41CC-A539-662EAA63D6AD}"/>
-    <hyperlink ref="J196" r:id="rId185" display="https://naturkundemuseum.erfurt.de/" xr:uid="{0E97A35F-D7DB-4CFA-BFE6-C84020D979F6}"/>
-    <hyperlink ref="J197" r:id="rId186" xr:uid="{9CB5A698-68A9-460F-AB91-0889A766C601}"/>
-    <hyperlink ref="J198" r:id="rId187" display="https://www.unb.br/" xr:uid="{34EA80D1-CAAB-46B0-B61F-D2D28B93482E}"/>
-    <hyperlink ref="J199" r:id="rId188" display="https://www.brukenthalmuseum.ro/" xr:uid="{ECCDD3D8-810D-4D4C-8C7D-C4A2D603B243}"/>
-    <hyperlink ref="J200" r:id="rId189" xr:uid="{65D2CC67-35E3-4B4E-8FAA-5C8BF95FF862}"/>
-    <hyperlink ref="J201" r:id="rId190" display="https://www.museo.fcnym.unlp.edu.ar/" xr:uid="{D61187DC-E61E-43AE-8CB1-B1F3FA8EC1BE}"/>
-    <hyperlink ref="J202" r:id="rId191" display="https://www.uni-tuebingen.de/" xr:uid="{04565327-740C-4479-ABA0-315082F9A2EC}"/>
-    <hyperlink ref="J204" r:id="rId192" display="https://www.hetnatuurmuseum.nl/" xr:uid="{460DA533-1069-4C14-84E1-718C205CBE5D}"/>
-    <hyperlink ref="J205" r:id="rId193" display="https://www.bates.edu/" xr:uid="{4A3A61D6-F39C-4459-8BBA-5DDC19917546}"/>
-    <hyperlink ref="J207" r:id="rId194" display="https://www.rmsc.org/" xr:uid="{39CBE7DD-C7A3-444F-A013-DF28CD561AE3}"/>
-    <hyperlink ref="J208" r:id="rId195" display="https://www.miami.edu/" xr:uid="{1F19E56B-8FE9-4CA7-B34B-8388C72ED36B}"/>
-    <hyperlink ref="J209" r:id="rId196" display="https://www.puc.edu/" xr:uid="{19690E92-156E-44FA-B3CB-4C615818F086}"/>
-    <hyperlink ref="J210" r:id="rId197" xr:uid="{70A6807C-4904-48B0-BCE6-2AB4086B9318}"/>
-    <hyperlink ref="J211" r:id="rId198" display="https://www.museocostarica.go.cr/" xr:uid="{49130A71-13D8-4FAC-9150-6376849D2FF5}"/>
-    <hyperlink ref="J212" r:id="rId199" xr:uid="{210BBFE2-43A4-41B4-B385-864F21D6C053}"/>
-    <hyperlink ref="J214" r:id="rId200" xr:uid="{772BD320-96E0-48B5-B589-0B7761B82653}"/>
-    <hyperlink ref="J215" r:id="rId201" display="https://www.nhmmaastricht.nl/" xr:uid="{6F987554-DA02-43A6-8BEB-7D1BBCED08B1}"/>
-    <hyperlink ref="J216" r:id="rId202" display="https://www.etsu.edu/" xr:uid="{33ABE461-3222-4DB4-89D2-8D4E8761E694}"/>
-    <hyperlink ref="J217" r:id="rId203" display="https://www.uwsp.edu/" xr:uid="{24197401-9451-441A-BD74-64CAA6572781}"/>
-    <hyperlink ref="J218" r:id="rId204" display="https://www.royalsaskmuseum.ca/" xr:uid="{5F7CFAD2-AEE5-4357-8582-FD5279FA1D11}"/>
-    <hyperlink ref="J219" r:id="rId205" display="https://www.tmag.tas.gov.au/" xr:uid="{8A94E683-D174-40A3-B91D-4BE5B27023E3}"/>
-    <hyperlink ref="J220" r:id="rId206" display="https://www.zzpsnv.rs/" xr:uid="{65E3FDCD-FA84-44BC-9471-546616609A41}"/>
-    <hyperlink ref="J221" r:id="rId207" display="https://www.zzps.rs/" xr:uid="{3995631B-738D-45F2-B14F-DA08125BEB0B}"/>
-    <hyperlink ref="J222" r:id="rId208" display="https://www.zmmu.msu.ru/" xr:uid="{E4D35DF5-8804-400E-A1D2-2F291046B707}"/>
-    <hyperlink ref="J223" r:id="rId209" display="https://www.coe.edu/" xr:uid="{2B7242B1-9CBC-495E-A6FC-19669388EC0D}"/>
-    <hyperlink ref="J224" r:id="rId210" xr:uid="{B7E1C0CF-9E9C-45E1-80E7-F4DCD0EFD7FC}"/>
-    <hyperlink ref="J225" r:id="rId211" display="https://www.pem.org/" xr:uid="{DFD520A5-9842-4E85-BC25-8C7AA6AE75C6}"/>
-    <hyperlink ref="J226" r:id="rId212" display="https://www.isu.edu/" xr:uid="{88ED022B-FAA2-4DD7-BD3E-708D562CA6C5}"/>
-    <hyperlink ref="J227" r:id="rId213" display="https://museum.novascotia.ca/" xr:uid="{09C4F7BB-1580-48C9-874E-F25A447A14E6}"/>
-    <hyperlink ref="J228" r:id="rId214" display="https://www.msn.unipi.it/" xr:uid="{143A1A3B-7C4E-4C2A-8C99-E13D436B20F0}"/>
-    <hyperlink ref="J229" r:id="rId215" display="https://www.fsu.edu/" xr:uid="{A6C34837-3B7C-422F-844A-C429ABDAE5A0}"/>
-    <hyperlink ref="J230" r:id="rId216" display="https://www.umaine.edu/" xr:uid="{2E349BBA-7F9B-4F77-B346-AD8021001518}"/>
-    <hyperlink ref="J231" r:id="rId217" display="https://www.museum-joanneum.at/" xr:uid="{600E1794-3385-465B-BAA5-8E0AF62E33EA}"/>
-    <hyperlink ref="J232" r:id="rId218" display="https://www.msn.unifi.it/" xr:uid="{5F9EB4BF-F109-498C-B6FE-75B252D210A2}"/>
-    <hyperlink ref="J233" r:id="rId219" display="https://www.putnam.org/" xr:uid="{1B71EE03-5624-4D37-88C3-D280FAA37AA8}"/>
-    <hyperlink ref="J235" r:id="rId220" display="https://www.manitobamuseum.ca/" xr:uid="{380D97D6-A7FD-4651-97DD-F6EF8036A57F}"/>
-    <hyperlink ref="J236" r:id="rId221" display="https://www.museodizoologia.it/" xr:uid="{2535626C-F904-47FA-B589-BEEFDA483F24}"/>
-    <hyperlink ref="J237" r:id="rId222" display="https://www.utm.edu/" xr:uid="{BFDEE8EC-CEDC-46A3-800D-CF7A2F76C5BD}"/>
-    <hyperlink ref="J240" r:id="rId223" display="https://www.natuurmuseumfriesland.nl/" xr:uid="{D325246E-5384-432D-B076-7AF13FBD1D56}"/>
-    <hyperlink ref="J241" r:id="rId224" display="https://www.museu-goeldi.br/" xr:uid="{F0F41BF6-5F9A-4E7E-8148-CA7A43E34DC7}"/>
-    <hyperlink ref="J242" r:id="rId225" display="https://zoology.muohio.edu/" xr:uid="{87D49761-F259-4A73-B4B7-E86670F8BFB4}"/>
-    <hyperlink ref="J243" r:id="rId226" xr:uid="{5D492783-D3E4-4F8C-8F07-8A6A0F65F136}"/>
-    <hyperlink ref="J244" r:id="rId227" display="https://www.mnhn.lu/" xr:uid="{23A8F790-E901-4E0B-8C5E-7C97D486931F}"/>
-    <hyperlink ref="J245" r:id="rId228" display="https://www.southendmuseums.co.uk/" xr:uid="{6549E7EF-4881-4574-A13F-7E9CC961C85D}"/>
-    <hyperlink ref="J246" r:id="rId229" display="https://museum.msu.edu/" xr:uid="{93AD35A1-0355-4A90-B722-B5CA4BA17414}"/>
-    <hyperlink ref="J247" r:id="rId230" display="https://www.msstate.edu/" xr:uid="{B8001B32-6A33-40A2-BFEF-9A0775F8FC0A}"/>
-    <hyperlink ref="J248" r:id="rId231" display="https://www.ecotarium.org/" xr:uid="{9A3112B0-2934-4128-811D-DF8C6DAC3B4D}"/>
-    <hyperlink ref="J249" r:id="rId232" display="https://www.fortworthmuseum.org/" xr:uid="{A088BEBC-9157-4083-8B1F-CFC59D7DEB45}"/>
-    <hyperlink ref="J251" r:id="rId233" xr:uid="{D1210697-1921-4797-9B46-C0563BD4BA3C}"/>
-    <hyperlink ref="J252" r:id="rId234" display="https://www.calstate.edu/" xr:uid="{F90FA497-83A2-4E1C-A54F-1C87C2B7EE60}"/>
-    <hyperlink ref="J253" r:id="rId235" display="https://www.sfasu.edu/" xr:uid="{A484141B-0A27-4557-B285-FBA62F83D48F}"/>
-    <hyperlink ref="J254" r:id="rId236" display="https://www.wallawalla.edu/" xr:uid="{CC5A3A51-9EF1-4780-9F2B-CF23300B82DB}"/>
-    <hyperlink ref="J255" r:id="rId237" display="https://www.museum-grenoble.fr/" xr:uid="{17A5C734-771E-41EC-89B2-F221365C3A21}"/>
-    <hyperlink ref="J256" r:id="rId238" display="https://www.vmo.cz/" xr:uid="{B09003D3-FF28-46B2-8C5E-30143F04982D}"/>
-    <hyperlink ref="J257" r:id="rId239" display="https://www.canterburymuseum.com/" xr:uid="{498AC590-C269-49A6-AE77-1F2BB79CAD16}"/>
-    <hyperlink ref="J258" r:id="rId240" display="https://naturalhistory.si.edu/" xr:uid="{AFA4DC46-CCE2-44EF-A0C9-059B25524ADE}"/>
-    <hyperlink ref="J259" r:id="rId241" display="https://www.cincymuseum.org/" xr:uid="{C2DD6FF6-F1B8-465C-87C1-E40B7BDE0034}"/>
-    <hyperlink ref="J260" r:id="rId242" display="https://www.colostate.edu/" xr:uid="{9B55902F-6CB9-441B-A395-57D0E652F65E}"/>
-    <hyperlink ref="J262" r:id="rId243" xr:uid="{49E0C3B6-485B-4835-AFA6-4BDBA1F3035B}"/>
-    <hyperlink ref="J263" r:id="rId244" display="https://www.mauritianum.de/" xr:uid="{E888E3B3-B480-4D01-A2BB-62B0996E19E0}"/>
-    <hyperlink ref="J264" r:id="rId245" display="https://www.swanseamuseum.co.uk/" xr:uid="{333421C9-F96A-42B3-858D-30BF7E154FEB}"/>
-    <hyperlink ref="J265" r:id="rId246" display="https://www.almnh.ua.edu/" xr:uid="{6AA1A41C-DC68-4484-AFB4-E388E5D94300}"/>
-    <hyperlink ref="J266" r:id="rId247" display="https://www.wagnerfreeinstitute.org/" xr:uid="{653E6324-A9D0-45FF-BA82-C2E333069B6A}"/>
-    <hyperlink ref="J267" r:id="rId248" display="https://www.minotstateu.edu/" xr:uid="{7CB71F6C-C168-43B6-B7CF-4241CD2CEFE7}"/>
-    <hyperlink ref="J268" r:id="rId249" display="https://www.sdstate.edu/" xr:uid="{9587F063-2AF4-43F4-9431-8E2FE2918249}"/>
-    <hyperlink ref="J269" r:id="rId250" display="https://www.museum.bamberg.de/" xr:uid="{9F149002-E834-4A2C-8901-08EE1C7EE25E}"/>
-    <hyperlink ref="J270" r:id="rId251" display="https://www.muzeumkarkonoskie.pl/" xr:uid="{BB98D610-6B3F-4E0C-A644-9645AF865544}"/>
-    <hyperlink ref="J271" r:id="rId252" display="https://www.yamashina.or.jp/" xr:uid="{C3365A3E-540F-435E-956B-1F5FCF4B8C0E}"/>
-    <hyperlink ref="J272" r:id="rId253" display="https://www.zin.ru/" xr:uid="{5D88D5B2-EE8B-4171-8A75-7E2D0D0A76FB}"/>
-    <hyperlink ref="J273" r:id="rId254" display="https://www.mncn.csic.es/" xr:uid="{F696B4B6-6EB5-435D-AB13-8839C7FE083A}"/>
-    <hyperlink ref="J274" r:id="rId255" display="https://www.isprambiente.gov.it/" xr:uid="{46B340B4-AFE4-47B6-849B-73221861E924}"/>
-    <hyperlink ref="J275" r:id="rId256" xr:uid="{2AF5EB49-551B-43EA-B8A6-59DF62B69317}"/>
-    <hyperlink ref="J276" r:id="rId257" display="https://www.tatmuseum.ru/" xr:uid="{01490A60-E851-48FA-B7F1-FBC02CDEFFE9}"/>
-    <hyperlink ref="J277" r:id="rId258" xr:uid="{1C5CCED0-022E-479F-8B95-EBBB864F479D}"/>
-    <hyperlink ref="J278" r:id="rId259" xr:uid="{22731A82-4B71-4C07-BD08-066CF8F6D3C1}"/>
-    <hyperlink ref="J279" r:id="rId260" display="https://www.bpn.com.pl/" xr:uid="{324B9E28-ADCE-4E94-8161-5DF403493786}"/>
-    <hyperlink ref="J281" r:id="rId261" display="https://www.aquasis.org/" xr:uid="{BAA9A816-8CCD-4449-98B3-3A9609B41D8E}"/>
-    <hyperlink ref="J282" r:id="rId262" display="https://www.fzb.rs.gov.br/" xr:uid="{72E5E380-FDEF-4D8E-B9D3-0A471DAEE1EC}"/>
-    <hyperlink ref="J283" r:id="rId263" display="https://www.icn.unal.edu.co/" xr:uid="{25D7F4C7-8817-4353-95A4-C93BC9FDD8C1}"/>
-    <hyperlink ref="J284" r:id="rId264" display="https://www.museodoria.it/" xr:uid="{ED44EF6C-4230-4EC6-8E35-E681B59BD262}"/>
-    <hyperlink ref="J286" r:id="rId265" display="https://www.vogelwarte-helgoland.de/" xr:uid="{B7B5A939-BB28-402C-8834-079175BD4A7E}"/>
-    <hyperlink ref="J289" r:id="rId266" display="https://www.muzeumvychodocesky.cz/" xr:uid="{3921485D-9E57-44FD-BE75-4EA08585E54A}"/>
-    <hyperlink ref="J291" r:id="rId267" display="https://www.biodokumentation.de/" xr:uid="{E0890B9B-0C81-46A6-A293-B4F60F7139CE}"/>
-    <hyperlink ref="J292" r:id="rId268" display="https://www.krskmuseum.ru/" xr:uid="{DD7F713B-A06D-47DF-AB5F-40A1CA5FFE0B}"/>
-    <hyperlink ref="J293" r:id="rId269" display="https://www.mnhn.cl/" xr:uid="{879C8588-8F0E-4944-9213-37B45A6F344A}"/>
-    <hyperlink ref="J294" r:id="rId270" display="https://www.coleccionphelps.org/" xr:uid="{218E870E-A8CD-4A76-8F59-4806EB1F2F78}"/>
-    <hyperlink ref="J295" r:id="rId271" display="https://www.ulasalle.ac.cr/" xr:uid="{ACBBF2E1-47C3-4A2C-B1D7-1CDC032BBFCA}"/>
-    <hyperlink ref="J297" r:id="rId272" xr:uid="{5400B104-383B-4C7B-ACAA-37E962D86E58}"/>
-    <hyperlink ref="J298" r:id="rId273" display="https://www.uaem.mx/" xr:uid="{7F92BC12-08AA-4426-B789-0B4C37820682}"/>
-    <hyperlink ref="J299" r:id="rId274" display="https://www.magnt.net.au/" xr:uid="{9C3FF8BA-203A-430C-A79D-880C5A4E0EB4}"/>
-    <hyperlink ref="J301" r:id="rId275" xr:uid="{CEF0ECFD-51A9-48E9-B29A-9387283DFC8F}"/>
-    <hyperlink ref="J302" r:id="rId276" xr:uid="{2A4D7391-786F-4B3E-ADF6-6B7E03BFF775}"/>
-    <hyperlink ref="J303" r:id="rId277" display="https://www.dmns.org/" xr:uid="{FD7DC1ED-0D4F-413E-B9AB-6624B2E706AC}"/>
-    <hyperlink ref="J304" r:id="rId278" xr:uid="{B0DF760A-6C14-46D2-8CE1-B410EC8FAAF3}"/>
-    <hyperlink ref="J305" r:id="rId279" display="https://samnoblemuseum.ou.edu/" xr:uid="{22619E57-7986-4C0C-A8F4-BCA9E89A4422}"/>
-    <hyperlink ref="J306" r:id="rId280" xr:uid="{DF650C73-3369-483B-B232-2E976E9795E7}"/>
-    <hyperlink ref="J307" r:id="rId281" xr:uid="{EF0CCDCF-44DF-4209-8EF1-FAF7DB5C0A10}"/>
+    <hyperlink ref="J307" r:id="rId1" xr:uid="{EF0CCDCF-44DF-4209-8EF1-FAF7DB5C0A10}"/>
+    <hyperlink ref="J2" r:id="rId2" display="https://www.nhm.ac.uk/" xr:uid="{2C38313E-5347-4665-969B-A4049313DB1F}"/>
+    <hyperlink ref="J3" r:id="rId3" display="https://wfvz.org/" xr:uid="{3A29E438-943E-4734-A4F5-986A21965842}"/>
+    <hyperlink ref="J4" r:id="rId4" display="https://www.zfmk.de/" xr:uid="{20711427-2227-4DF7-B858-0094F952210F}"/>
+    <hyperlink ref="J5" r:id="rId5" display="https://www.museumfuernaturkunde.berlin/" xr:uid="{9D9CF323-089F-4F22-A6FF-71EDD3F9C5B2}"/>
+    <hyperlink ref="J6" r:id="rId6" display="https://www.nms.ac.uk/" xr:uid="{151102B7-3919-4F55-8AF9-642CF81B9352}"/>
+    <hyperlink ref="J7" r:id="rId7" display="https://www.naturalis.nl/" xr:uid="{314919E4-51BF-41A3-8824-805231A239B8}"/>
+    <hyperlink ref="J8" r:id="rId8" display="https://delmns.org/" xr:uid="{9A9AB608-FA85-4D8E-87B5-084CBBB1DFB0}"/>
+    <hyperlink ref="J9" r:id="rId9" display="https://naturalhistory.si.edu/" xr:uid="{C85A6226-CE44-4B69-9A6B-F133AF3C7DC0}"/>
+    <hyperlink ref="J10" r:id="rId10" display="https://www.luomus.fi/" xr:uid="{CB9A256E-6652-4BB6-AFC1-5408472717C8}"/>
+    <hyperlink ref="J11" r:id="rId11" display="https://www.nrm.se/" xr:uid="{DD8D5251-31A3-4E82-AE93-BBC12F7F3619}"/>
+    <hyperlink ref="J12" r:id="rId12" xr:uid="{917FDED8-9B8A-43B3-B90F-260ABE657829}"/>
+    <hyperlink ref="J13" r:id="rId13" xr:uid="{41A7C5B2-D7E6-4DCE-B643-160F24E790E7}"/>
+    <hyperlink ref="J14" r:id="rId14" xr:uid="{09664DC3-4964-44A3-823E-9A7A5788AAFD}"/>
+    <hyperlink ref="J15" r:id="rId15" display="https://www.fieldmuseum.org/" xr:uid="{AE834FBA-55B3-45FC-A10E-DD9BE9AB63BC}"/>
+    <hyperlink ref="J16" r:id="rId16" display="https://www.australianmuseum.net.au/" xr:uid="{80D292D9-7F79-4C53-83C9-6DE9B17D0A04}"/>
+    <hyperlink ref="J17" r:id="rId17" display="https://www.3landesmuseen.de/" xr:uid="{53A4FC7A-99D0-46C2-B714-BC25C077844F}"/>
+    <hyperlink ref="J18" r:id="rId18" xr:uid="{D339EC37-2984-46E3-A9E4-C3276555C51E}"/>
+    <hyperlink ref="J19" r:id="rId19" xr:uid="{20A32808-DB4F-463D-BA8B-3CE3D86D40A6}"/>
+    <hyperlink ref="J20" r:id="rId20" xr:uid="{7DFDD0B8-B788-48AB-9E72-E4CAD3560547}"/>
+    <hyperlink ref="J21" r:id="rId21" display="https://www.amnh.org/" xr:uid="{BDE61E15-8651-408C-B2A9-71BACF213117}"/>
+    <hyperlink ref="J22" r:id="rId22" display="https://www.senckenberg.de/" xr:uid="{A83EBDE5-6FD7-428C-BF1D-DE5A1A5A27D9}"/>
+    <hyperlink ref="J23" r:id="rId23" display="https://www.royalalbertamuseum.ca/" xr:uid="{AF8FCE8F-F952-4FC3-A532-A1FC7D7E1389}"/>
+    <hyperlink ref="J24" r:id="rId24" display="https://mvz.berkeley.edu/" xr:uid="{CA4982BF-143D-43D2-BBFC-C005BC15F806}"/>
+    <hyperlink ref="J25" r:id="rId25" display="https://peabody.yale.edu/" xr:uid="{4EF31E43-D8FB-4C65-960B-169E3B6749A6}"/>
+    <hyperlink ref="J26" r:id="rId26" display="https://www.nhm-wien.ac.at/" xr:uid="{CC3D0F74-A166-4A49-834C-58EE03B55945}"/>
+    <hyperlink ref="J27" r:id="rId27" xr:uid="{3C962FEC-F2F2-42A9-BEFD-D5D42D167CD5}"/>
+    <hyperlink ref="J29" r:id="rId28" display="https://www.uwgb.edu/" xr:uid="{DC06165E-8D90-455F-89A3-126D17A6EB8C}"/>
+    <hyperlink ref="J30" r:id="rId29" display="https://www.landesmuseum-hannover.de/" xr:uid="{7581783D-FD4C-4BCD-BB9A-6F0703683E3B}"/>
+    <hyperlink ref="J31" r:id="rId30" display="https://mcz.harvard.edu/" xr:uid="{BD4DEFC6-8E7E-4FF6-AFCA-D88F8511BC13}"/>
+    <hyperlink ref="J32" r:id="rId31" display="https://www.museum.manchester.ac.uk/" xr:uid="{AA03BBB5-66CB-45D9-8193-30F021E4AB70}"/>
+    <hyperlink ref="J33" r:id="rId32" display="https://www.rom.on.ca/" xr:uid="{A41C9F7B-4517-4A30-8F34-FA9525820653}"/>
+    <hyperlink ref="J34" r:id="rId33" display="https://www.floridamuseum.ufl.edu/" xr:uid="{047BDDBF-4381-485F-94D8-EF5B8C50FC57}"/>
+    <hyperlink ref="J35" r:id="rId34" display="https://www.naturkundemuseum-bw.de/" xr:uid="{4BBC8996-2CF3-4644-8066-BFC1B8652BD8}"/>
+    <hyperlink ref="J36" r:id="rId35" xr:uid="{C3C31F64-E1CE-443D-B13F-71D02F8EE28E}"/>
+    <hyperlink ref="J37" r:id="rId36" xr:uid="{5FE5F3EA-D747-4C7E-BB3C-412BF68E4EC8}"/>
+    <hyperlink ref="J38" r:id="rId37" xr:uid="{49FF97B8-E685-4F3F-9C78-3DB2F2FD536C}"/>
+    <hyperlink ref="J39" r:id="rId38" xr:uid="{E3062415-8261-4C40-88C5-E2B397D4028A}"/>
+    <hyperlink ref="J40" r:id="rId39" display="https://greatnorthmuseum.org.uk/" xr:uid="{160AF23E-7BA0-4D07-93FD-FEB5729EA899}"/>
+    <hyperlink ref="J41" r:id="rId40" xr:uid="{089A682B-0862-46EA-B239-46BC11A27085}"/>
+    <hyperlink ref="J42" r:id="rId41" display="https://www.sbnature.org/" xr:uid="{ED993E2A-5BEE-4CFB-9D5A-116DD89719E0}"/>
+    <hyperlink ref="J43" r:id="rId42" xr:uid="{1879E9D6-C999-4085-80CC-EAAF3DF9387B}"/>
+    <hyperlink ref="J44" r:id="rId43" display="https://www.ditsong.org.za/" xr:uid="{4C8BDE58-F508-4A27-B71D-36B396F63E4E}"/>
+    <hyperlink ref="J45" r:id="rId44" display="https://www.nmbe.ch/" xr:uid="{80730FDE-2E7B-48CA-B7E9-69A25548266B}"/>
+    <hyperlink ref="J46" r:id="rId45" xr:uid="{7DFF857F-C22F-4CBF-A2F9-985AC932F7B0}"/>
+    <hyperlink ref="J47" r:id="rId46" xr:uid="{C4B97B47-CAEA-49B9-8319-1DE935701A66}"/>
+    <hyperlink ref="J48" r:id="rId47" xr:uid="{A2F58E72-A17A-470D-A8A7-B3799FFA6A34}"/>
+    <hyperlink ref="J49" r:id="rId48" display="https://museum.wales/" xr:uid="{70DC7129-9859-4734-8CE7-C4EDA8032E2E}"/>
+    <hyperlink ref="J50" r:id="rId49" display="https://www.museum.zoo.cam.ac.uk/" xr:uid="{772B9A52-8978-410F-AD3D-50CB3D6BF016}"/>
+    <hyperlink ref="J51" r:id="rId50" xr:uid="{D58A8E5D-41A0-4E1D-B4C6-0F39AA67AEF2}"/>
+    <hyperlink ref="J52" r:id="rId51" display="https://www.calacademy.org/" xr:uid="{B9DBD6E6-8818-4E7E-8506-9AAAAF55D01B}"/>
+    <hyperlink ref="J53" r:id="rId52" xr:uid="{479C10FB-5851-484B-BAA1-1E304DA7BCBB}"/>
+    <hyperlink ref="J54" r:id="rId53" xr:uid="{FB59B757-11A1-410E-AB62-DD653E88C504}"/>
+    <hyperlink ref="J55" r:id="rId54" display="https://www.samuseum.sa.gov.au/" xr:uid="{7C5CE76D-7358-4BB7-B4DC-F4ABCABFF1B4}"/>
+    <hyperlink ref="J56" r:id="rId55" display="https://museumsvictoria.com.au/" xr:uid="{3FAFABEB-9A18-4296-9AB0-248A78B81A47}"/>
+    <hyperlink ref="J57" r:id="rId56" xr:uid="{61239945-B7F5-4BB9-A6D4-3F08D090F6CF}"/>
+    <hyperlink ref="J58" r:id="rId57" display="https://www.umass.edu/" xr:uid="{2FF63480-E048-4433-AB08-C5EB30782D22}"/>
+    <hyperlink ref="J59" r:id="rId58" display="https://www.meeresmuseum.de/" xr:uid="{EB642B2A-399C-4FEA-8CC3-919AD8D0880E}"/>
+    <hyperlink ref="J60" r:id="rId59" display="https://www.nysm.nysed.gov/" xr:uid="{B44B691F-73E6-43B4-B033-7DA872433F71}"/>
+    <hyperlink ref="J61" r:id="rId60" display="https://www.boltonlams.co.uk/" xr:uid="{3467C001-CC55-4516-B865-6A71C7F4AED3}"/>
+    <hyperlink ref="J62" r:id="rId61" display="https://www.clemson.edu/" xr:uid="{87F6F2A0-88B7-483D-B636-0ECAF70F2187}"/>
+    <hyperlink ref="J63" r:id="rId62" display="https://www.naturkundemuseum.leipzig.de/" xr:uid="{B5E22082-9D49-42DE-A27E-C5776C38D8FC}"/>
+    <hyperlink ref="J64" r:id="rId63" display="https://www.senckenberg.de/" xr:uid="{20B40E08-82C9-4CA5-A7C1-06DF5317C21E}"/>
+    <hyperlink ref="J65" r:id="rId64" display="https://www.nm.cz/" xr:uid="{8E89893D-F07F-49B0-934E-1F123724D652}"/>
+    <hyperlink ref="J66" r:id="rId65" display="https://www.mnhn.fr/" xr:uid="{BBC1691A-C79B-40A6-9EF6-20CBD3E6AF1C}"/>
+    <hyperlink ref="J67" r:id="rId66" xr:uid="{F915223D-F55D-4194-A2BB-F9DC657061D3}"/>
+    <hyperlink ref="J68" r:id="rId67" display="https://www.readingmuseum.org.uk/" xr:uid="{6CD2E081-A227-4B39-B7DA-3E6E168EEA72}"/>
+    <hyperlink ref="J69" r:id="rId68" xr:uid="{460949AD-835A-4646-B61C-9DB4AF29FD8E}"/>
+    <hyperlink ref="J70" r:id="rId69" xr:uid="{5D30F181-159A-4471-AB73-76AD0F08445A}"/>
+    <hyperlink ref="J71" r:id="rId70" display="https://www.burkemuseum.org/" xr:uid="{B7E3D66C-9E0C-407C-8D55-18A7FEA27421}"/>
+    <hyperlink ref="J72" r:id="rId71" display="https://www.humboldt.org.co/" xr:uid="{E40D940A-9E21-4B23-8F11-072396631F09}"/>
+    <hyperlink ref="J73" r:id="rId72" xr:uid="{113AD29A-7034-42DE-AD4F-C2F9AC2CA454}"/>
+    <hyperlink ref="J74" r:id="rId73" display="https://www.nhm-rudolstadt.de/" xr:uid="{086C7DD7-EDA0-4645-BC3F-DA469F870B29}"/>
+    <hyperlink ref="J75" r:id="rId74" display="https://www.illinoisstatemuseum.org/" xr:uid="{C9428D01-04CF-4156-9EAF-AD50391A43DF}"/>
+    <hyperlink ref="J76" r:id="rId75" xr:uid="{EC81FCBC-DFE4-4403-9C8C-E101455C2809}"/>
+    <hyperlink ref="J77" r:id="rId76" display="https://www.dmns.org/" xr:uid="{A48F09AC-C275-4553-943A-19269F311835}"/>
+    <hyperlink ref="J78" r:id="rId77" xr:uid="{939CA8C7-8D4C-45BB-A46E-1CA60C0D9B74}"/>
+    <hyperlink ref="J79" r:id="rId78" xr:uid="{B908215F-10D1-4780-A569-E0EEE403F18A}"/>
+    <hyperlink ref="J80" r:id="rId79" display="https://www.mueritzeum.de/" xr:uid="{68879A95-25AD-4EB5-92B7-15129A544087}"/>
+    <hyperlink ref="J81" r:id="rId80" xr:uid="{8175DED2-EF8C-4F35-AE5F-2E1B88419221}"/>
+    <hyperlink ref="J83" r:id="rId81" display="https://www.charlestonmuseum.org/" xr:uid="{ED440609-97C3-4FB6-AE00-F0B5A8AF98B3}"/>
+    <hyperlink ref="J84" r:id="rId82" display="https://samnoblemuseum.ou.edu/" xr:uid="{733EDFAB-B79A-4F7D-AC88-543EFACBE002}"/>
+    <hyperlink ref="J85" r:id="rId83" xr:uid="{E7BBD58B-0CE9-4405-8F8B-94E4617CF2FD}"/>
+    <hyperlink ref="J86" r:id="rId84" display="https://www.tulliehouse.co.uk/" xr:uid="{E8D18027-1CCB-47C8-BCA1-426A0CD3E160}"/>
+    <hyperlink ref="J87" r:id="rId85" display="https://www.welderwildlife.org/" xr:uid="{4D4B79F9-D593-4CAC-8A01-B0633959F875}"/>
+    <hyperlink ref="J88" r:id="rId86" display="https://www.uebersee-museum.de/" xr:uid="{7E2715BB-2F24-4E7E-A95C-9C32F2A206B3}"/>
+    <hyperlink ref="J89" r:id="rId87" display="https://www.theherbert.org/" xr:uid="{7EBB27A5-C341-4D97-A1AC-A93C6454BD19}"/>
+    <hyperlink ref="J90" r:id="rId88" xr:uid="{ADA5AA4D-81D0-4952-81E7-25D59A320829}"/>
+    <hyperlink ref="J91" r:id="rId89" xr:uid="{F1AC4850-252C-4580-8CC1-9FCAFA09FF3B}"/>
+    <hyperlink ref="J92" r:id="rId90" display="https://www.naturkunde-museum-coburg.de/" xr:uid="{30C175CF-615B-4733-8BB6-181DB807C66D}"/>
+    <hyperlink ref="J93" r:id="rId91" display="https://museumsandgalleries.leeds.gov.uk/" xr:uid="{563D2EB6-7556-46BB-AD57-A90674CB2E3A}"/>
+    <hyperlink ref="J94" r:id="rId92" display="https://www.isez.pan.krakow.pl/" xr:uid="{8B52977A-AC4A-4BAC-B61A-0C7E1758F1A8}"/>
+    <hyperlink ref="J95" r:id="rId93" display="https://www.tulsazoo.org/" xr:uid="{EE9AE305-A360-4207-BBD7-45558EBC77B7}"/>
+    <hyperlink ref="J96" r:id="rId94" xr:uid="{DA461459-4F48-4FA2-94EE-8326019FBB5F}"/>
+    <hyperlink ref="J97" r:id="rId95" xr:uid="{3D08C7F2-99D4-413C-B0F2-CB28A3D925F3}"/>
+    <hyperlink ref="J98" r:id="rId96" display="https://www.naturundmensch.de/" xr:uid="{5DA7E8ED-BEDD-4F2E-847B-EEE3C8F4811F}"/>
+    <hyperlink ref="J99" r:id="rId97" xr:uid="{44E09F01-2635-4B28-BCDE-4CA1CE3C9F14}"/>
+    <hyperlink ref="J100" r:id="rId98" xr:uid="{FD93C8A7-3FBA-4090-B92C-230BC44DB2AD}"/>
+    <hyperlink ref="J102" r:id="rId99" display="https://mlbean.byu.edu/" xr:uid="{750E844B-1999-4112-B487-5F7A6AC5CF35}"/>
+    <hyperlink ref="J103" r:id="rId100" display="https://www.bristolmuseums.org.uk/" xr:uid="{3E5B8D39-C086-4FDD-9562-05BFEE6E273A}"/>
+    <hyperlink ref="J104" r:id="rId101" xr:uid="{A88F6B65-A6D5-4FC7-82CD-7CD05E631C6E}"/>
+    <hyperlink ref="J105" r:id="rId102" display="https://www.senckenberg.de/" xr:uid="{0D0008B0-68BD-4292-B406-AE3347E8FA0C}"/>
+    <hyperlink ref="J106" r:id="rId103" xr:uid="{4ECCAD3E-8841-405F-9F25-169326EBFC25}"/>
+    <hyperlink ref="J107" r:id="rId104" display="https://www.unr.edu/" xr:uid="{0FF210CA-9AF1-4C56-B726-FC2CE2CE5532}"/>
+    <hyperlink ref="J108" r:id="rId105" display="https://www.saffronwaldenmuseum.org/" xr:uid="{2A78EEBB-6102-452D-BAF9-0289C34C5197}"/>
+    <hyperlink ref="J110" r:id="rId106" display="https://www.mpm.edu/" xr:uid="{D20FE161-2A0F-41F8-B218-8CC4926BACF2}"/>
+    <hyperlink ref="J111" r:id="rId107" xr:uid="{B850BA8C-A51F-4C82-A32C-63CFDD37F30C}"/>
+    <hyperlink ref="J112" r:id="rId108" display="https://www.vt.edu/" xr:uid="{B577B818-FC5D-42F6-80D9-E6007AE67CA5}"/>
+    <hyperlink ref="J114" r:id="rId109" display="https://www.cmnh.org/" xr:uid="{B5AF784B-3F1B-432D-B79D-307553981260}"/>
+    <hyperlink ref="J115" r:id="rId110" xr:uid="{9FBF0BC5-19F5-4218-BA3C-DF21ABC2E721}"/>
+    <hyperlink ref="J116" r:id="rId111" xr:uid="{B352E4C5-0181-4271-AC4D-775666110F2A}"/>
+    <hyperlink ref="J117" r:id="rId112" display="https://www.oumnh.ox.ac.uk/" xr:uid="{35566483-00D1-4448-8DE9-728D7E13CE2C}"/>
+    <hyperlink ref="J118" r:id="rId113" xr:uid="{27FDB8DC-E2EC-4FD1-87FE-C86739CFFF25}"/>
+    <hyperlink ref="J119" r:id="rId114" display="https://biodiversity.ku.edu/" xr:uid="{3FBCF1A8-4B18-4A63-98A8-5DE4236C12FB}"/>
+    <hyperlink ref="J120" r:id="rId115" display="https://www.birds.cornell.edu/" xr:uid="{D51421E4-BEAF-46D8-BBF9-79AA4E4966BC}"/>
+    <hyperlink ref="J121" r:id="rId116" xr:uid="{BB6DFFF5-6A66-4BE8-898D-891B8BBA959A}"/>
+    <hyperlink ref="J122" r:id="rId117" display="https://www.museum.toulouse.fr/" xr:uid="{3A68202B-0E55-4C2C-BAA5-505D1A6F922A}"/>
+    <hyperlink ref="J123" r:id="rId118" display="https://www.museum.qld.gov.au/" xr:uid="{BBCBB14E-4F94-46B5-9A95-A50A2971FB0C}"/>
+    <hyperlink ref="J124" r:id="rId119" xr:uid="{9E9738C5-A9A0-4639-BBDC-0A92F5F51919}"/>
+    <hyperlink ref="J125" r:id="rId120" xr:uid="{1022F794-13B8-4834-8A67-B5F92BB1F79A}"/>
+    <hyperlink ref="J126" r:id="rId121" display="https://www.uark.edu/" xr:uid="{DFCB06AE-16AC-4320-BFAE-7D3BA64731EA}"/>
+    <hyperlink ref="J127" r:id="rId122" display="https://www.museum.wa.gov.au/" xr:uid="{71E776FD-7EB0-4123-8A43-50A8D9374B6D}"/>
+    <hyperlink ref="J128" r:id="rId123" display="https://www.sciencemuseum.org.uk/" xr:uid="{C9E0D3DB-94A1-4DBC-861F-51F8976CFE51}"/>
+    <hyperlink ref="J129" r:id="rId124" display="https://www.africamuseum.be/" xr:uid="{7F2BC1B2-B8CF-43A7-AD5A-FC04508F2594}"/>
+    <hyperlink ref="J130" r:id="rId125" xr:uid="{42FF65A2-0DD2-491C-8C7E-3209323D66AE}"/>
+    <hyperlink ref="J131" r:id="rId126" display="https://www.rammuseum.org.uk/" xr:uid="{4AFA0EFD-3D93-4ED9-A970-896A003A0AB6}"/>
+    <hyperlink ref="J132" r:id="rId127" display="https://cumuseum.colorado.edu/" xr:uid="{F764DD7B-75F4-4B57-B422-347C61D40AAF}"/>
+    <hyperlink ref="J133" r:id="rId128" display="https://www.tau.ac.il/" xr:uid="{961CF022-DF69-4714-9864-4742DCF6C20F}"/>
+    <hyperlink ref="J134" r:id="rId129" display="https://www.bellmuseum.umn.edu/" xr:uid="{5369A9BD-33FE-4483-A621-B50ED7511494}"/>
+    <hyperlink ref="J135" r:id="rId130" display="https://www.zemaljskimuzej.ba/" xr:uid="{7FAA3420-6A68-40A4-ACA4-CA5C596359B4}"/>
+    <hyperlink ref="J136" r:id="rId131" display="https://www.museum.unl.edu/" xr:uid="{5A9DFE64-171B-4D1F-9914-6E041FB59AEA}"/>
+    <hyperlink ref="J137" r:id="rId132" display="https://www.museumfuernaturkunde.berlin/" xr:uid="{37268C27-2AD5-42E3-9515-96941A3BFE31}"/>
+    <hyperlink ref="J138" r:id="rId133" display="https://www.ebd.csic.es/" xr:uid="{BD9FAB5A-16CC-4477-84C1-72780C935057}"/>
+    <hyperlink ref="J139" r:id="rId134" display="https://www.muzeum.bytom.pl/" xr:uid="{FE5772FB-88A6-43EA-89CE-E461E44B7D66}"/>
+    <hyperlink ref="J140" r:id="rId135" display="https://www.otagomuseum.nz/" xr:uid="{0016EFB6-63AB-4FBA-98CA-EF205AB1A719}"/>
+    <hyperlink ref="J141" r:id="rId136" display="https://www.naturkundemuseum-bw.de/" xr:uid="{1406F8F9-648F-42DF-A146-C1A7C21B2ED6}"/>
+    <hyperlink ref="J142" r:id="rId137" display="https://www.museum-westlausitz.de/" xr:uid="{80B80A44-3E1D-48C8-8D27-2D41D2B49B6B}"/>
+    <hyperlink ref="J143" r:id="rId138" display="https://www.antipa.ro/" xr:uid="{F145A0C8-8879-4B93-9017-80A96BFE46B9}"/>
+    <hyperlink ref="J144" r:id="rId139" display="https://www.vsmuzeum.sk/" xr:uid="{E3606FCC-84B9-472A-BF37-579FBF6E73E9}"/>
+    <hyperlink ref="J145" r:id="rId140" display="https://naturalhistory.si.edu/" xr:uid="{3624C16D-DD89-4895-9E1B-F3C8FCF30E1E}"/>
+    <hyperlink ref="J146" r:id="rId141" display="https://www.naturemuseum.org/" xr:uid="{4794647B-35A9-4E11-828A-2BCB006369BE}"/>
+    <hyperlink ref="J147" r:id="rId142" display="https://www.aucklandmuseum.com/" xr:uid="{595FDC3C-46C6-41A0-887F-4D69D1154152}"/>
+    <hyperlink ref="J148" r:id="rId143" xr:uid="{E927971B-3A64-4BAA-BF6A-0CA59E386A7B}"/>
+    <hyperlink ref="J149" r:id="rId144" display="https://www.ccmuseum.com/" xr:uid="{25EC264E-525F-4F83-AC9C-E844C67FC2F8}"/>
+    <hyperlink ref="J150" r:id="rId145" xr:uid="{1A19A9A9-4ECA-48B0-9552-AC3885A0C0C4}"/>
+    <hyperlink ref="J151" r:id="rId146" display="https://www.tepapa.govt.nz/" xr:uid="{7F937EE1-46DC-4F33-9F9A-94C8830E0433}"/>
+    <hyperlink ref="J152" r:id="rId147" display="https://www.museum-wiesbaden.de/" xr:uid="{138D81E3-3D2C-4274-9634-D1303404C1EC}"/>
+    <hyperlink ref="J153" r:id="rId148" xr:uid="{F7130F22-3BB7-4575-AE37-810F52FF8A0D}"/>
+    <hyperlink ref="J154" r:id="rId149" display="https://www.macnconicet.gob.ar/" xr:uid="{16195D03-7008-4E32-B5EF-EC2C2B2E75D2}"/>
+    <hyperlink ref="J155" r:id="rId150" display="https://www.museunacional.ufrj.br/" xr:uid="{4DCE007D-E434-4CC0-BFCA-96D6ADA0B89D}"/>
+    <hyperlink ref="J156" r:id="rId151" display="https://www.darwinmuseum.ru/" xr:uid="{91BCBD7D-6A0D-4178-AECD-290E07E3BF1D}"/>
+    <hyperlink ref="J157" r:id="rId152" display="https://www.birminghammuseums.org.uk/" xr:uid="{887E5237-F75D-4861-955A-48955833E80C}"/>
+    <hyperlink ref="J158" r:id="rId153" display="https://mnh.uiowa.edu/" xr:uid="{AD963DC0-6A93-458A-9E0B-AF4A9F48B397}"/>
+    <hyperlink ref="J159" r:id="rId154" display="https://www.fairbanksmuseum.org/" xr:uid="{E3B878BE-D8C7-42CE-9287-39BE0C360F88}"/>
+    <hyperlink ref="J160" r:id="rId155" display="https://mnch.uoregon.edu/" xr:uid="{4B11832B-7380-4C0B-90E0-5347AF899E3C}"/>
+    <hyperlink ref="J161" r:id="rId156" xr:uid="{AAE0401E-8394-43F6-8650-198557C8F16A}"/>
+    <hyperlink ref="J162" r:id="rId157" xr:uid="{316AD0FF-C9B4-4C14-B167-86C20A29D9BA}"/>
+    <hyperlink ref="J163" r:id="rId158" xr:uid="{95D52DDC-07A5-4359-AC33-BEDADDBBD45A}"/>
+    <hyperlink ref="J165" r:id="rId159" display="https://www.arizona.edu/" xr:uid="{1A9AF8AB-8B2E-486C-ABEF-8E89F532151B}"/>
+    <hyperlink ref="J166" r:id="rId160" xr:uid="{C9976AB7-C793-4143-A3FF-4743F1C36192}"/>
+    <hyperlink ref="J167" r:id="rId161" display="https://www.mos.org/" xr:uid="{E9A22395-F68E-4D38-8A28-B4F84DA24B84}"/>
+    <hyperlink ref="J168" r:id="rId162" xr:uid="{6F081D5C-454E-4809-99EF-AA047F930ACE}"/>
+    <hyperlink ref="J169" r:id="rId163" xr:uid="{515E1E73-EC0A-4C93-8EBD-93F39B24A6F4}"/>
+    <hyperlink ref="J170" r:id="rId164" display="https://www.qvmag.tas.gov.au/" xr:uid="{4DBCAAE3-1DE7-4852-A407-6ECBC7A42E27}"/>
+    <hyperlink ref="J171" r:id="rId165" display="https://www.zsm.mwn.de/" xr:uid="{4D9BC638-9489-4B3A-A4D9-332273B1327C}"/>
+    <hyperlink ref="J172" r:id="rId166" xr:uid="{9FE0A72D-5674-4156-A326-624F9E13224B}"/>
+    <hyperlink ref="J173" r:id="rId167" display="https://www.lillo.org.ar/" xr:uid="{2356411A-D3D2-4617-9626-9F9F1A573EA5}"/>
+    <hyperlink ref="J174" r:id="rId168" display="https://www.muzeumbardejov.sk/" xr:uid="{D47AB8E5-F5E5-41EF-80FD-AF4A0F07EEBB}"/>
+    <hyperlink ref="J175" r:id="rId169" xr:uid="{2F93B1A0-EA5B-4DE7-9594-31D6EBBFC850}"/>
+    <hyperlink ref="J176" r:id="rId170" display="https://biodiversity.uconn.edu/" xr:uid="{640BEAAC-5F24-431D-9AA7-A3E26F80A9DA}"/>
+    <hyperlink ref="J177" r:id="rId171" display="https://www.wisc.edu/" xr:uid="{20FE0970-91CD-4666-9944-ECB87FCEFA7A}"/>
+    <hyperlink ref="J178" r:id="rId172" display="https://www.usask.ca/" xr:uid="{260B6A1D-515A-4EEB-9EE8-58525D87FD43}"/>
+    <hyperlink ref="J180" r:id="rId173" display="https://inhs.illinois.edu/" xr:uid="{73AD0B2A-60F8-4E04-A71A-C03B968B28A0}"/>
+    <hyperlink ref="J181" r:id="rId174" display="https://www.unm.edu/" xr:uid="{8BC9D99A-35A1-4D74-9E50-5696E0B91416}"/>
+    <hyperlink ref="J182" r:id="rId175" display="https://www.museedesconfluences.fr/" xr:uid="{8D54CD84-822F-4F24-8551-64C80FA83AA8}"/>
+    <hyperlink ref="J183" r:id="rId176" display="https://statemuseumpa.org/" xr:uid="{048C60A9-CBE8-4BD3-B249-E0986222E4F0}"/>
+    <hyperlink ref="J184" r:id="rId177" display="https://www.sewanee.edu/" xr:uid="{62EB89A4-F6DD-4A9F-AE53-29A0E23D2EBB}"/>
+    <hyperlink ref="J185" r:id="rId178" xr:uid="{02CF60E8-E66F-48CA-8C3C-818C9F9FAFFF}"/>
+    <hyperlink ref="J186" r:id="rId179" display="https://www.humboldt.edu/" xr:uid="{5C398E96-2F64-4524-90FF-BE93F3B400A8}"/>
+    <hyperlink ref="J187" r:id="rId180" xr:uid="{DE433EF3-4CF6-42C2-90D2-0A31F70069E1}"/>
+    <hyperlink ref="J188" r:id="rId181" display="https://www.phyletisches-museum.uni-jena.de/" xr:uid="{229A1A18-25A9-43ED-9A74-09772589D235}"/>
+    <hyperlink ref="J189" r:id="rId182" display="https://www.yorkshiremuseum.org.uk/" xr:uid="{42C59EBA-BB48-44D7-8E9F-560B0CB024CE}"/>
+    <hyperlink ref="J190" r:id="rId183" display="https://www.sciencebuff.org/" xr:uid="{A7F32D9B-B61B-4D85-A09D-6A9FE659CA50}"/>
+    <hyperlink ref="J191" r:id="rId184" display="https://www.naturkundemuseum-bw.de/" xr:uid="{66FA873D-67AB-40EE-BAB2-D709531CA81F}"/>
+    <hyperlink ref="J192" r:id="rId185" display="https://www.bellmuseum.umn.edu/" xr:uid="{78910859-4563-4B6A-B676-0CE4589710F4}"/>
+    <hyperlink ref="J193" r:id="rId186" xr:uid="{0410CFC3-DC67-415F-8EEC-5A8BE1BADF42}"/>
+    <hyperlink ref="J194" r:id="rId187" display="https://www.adams.edu/" xr:uid="{D711975A-689E-4787-88A9-48A8FFD71E4C}"/>
+    <hyperlink ref="J195" r:id="rId188" xr:uid="{C239FAFB-A5F3-48B9-884C-C8BA1E1E3293}"/>
+    <hyperlink ref="J196" r:id="rId189" xr:uid="{02EEDBD9-96C5-4962-9098-63900038642C}"/>
+    <hyperlink ref="J197" r:id="rId190" xr:uid="{482287D0-C8CE-4260-8408-3C1CDAC812F2}"/>
+    <hyperlink ref="J198" r:id="rId191" display="https://www.unb.br/" xr:uid="{BC10B19A-E9B1-40D7-B7A0-B7A98818D9C9}"/>
+    <hyperlink ref="J199" r:id="rId192" display="https://www.brukenthalmuseum.ro/" xr:uid="{0FA0A20A-3225-4CEB-ACA0-874C595682FB}"/>
+    <hyperlink ref="J200" r:id="rId193" xr:uid="{71D8B9BB-731B-4F54-993A-5CBB08440E7A}"/>
+    <hyperlink ref="J201" r:id="rId194" display="https://www.museo.fcnym.unlp.edu.ar/" xr:uid="{A10BCD43-3EB3-425B-856C-2F2072DE0A6B}"/>
+    <hyperlink ref="J202" r:id="rId195" display="https://www.uni-tuebingen.de/" xr:uid="{9A5A8E2F-4779-4590-A785-40D803706EF0}"/>
+    <hyperlink ref="J203" r:id="rId196" xr:uid="{3FC66E2C-1A01-4A55-A2E9-FF562819816D}"/>
+    <hyperlink ref="J204" r:id="rId197" xr:uid="{CDCF9738-80CF-4172-BB83-8D82FA9BC69C}"/>
+    <hyperlink ref="J205" r:id="rId198" display="https://www.bates.edu/" xr:uid="{C118157D-71BE-4864-AFAB-34321E53E7CC}"/>
+    <hyperlink ref="J206" r:id="rId199" xr:uid="{3E9EA6BD-DAC3-464D-BD7D-70125664B758}"/>
+    <hyperlink ref="J207" r:id="rId200" display="https://www.rmsc.org/" xr:uid="{42E099E3-49E6-4A5D-8EF5-00CA1B4E546B}"/>
+    <hyperlink ref="J208" r:id="rId201" display="https://www.miami.edu/" xr:uid="{4CD84ED6-B2AE-4B84-AC4A-1E3B9C2F39FE}"/>
+    <hyperlink ref="J209" r:id="rId202" display="https://www.puc.edu/" xr:uid="{A474C85A-8206-4191-B20F-2DD07B973624}"/>
+    <hyperlink ref="J210" r:id="rId203" xr:uid="{1C0969E0-37F9-498C-A6B6-05E5DF44B8A5}"/>
+    <hyperlink ref="J211" r:id="rId204" display="https://www.museocostarica.go.cr/" xr:uid="{6A6186BC-20A4-4D12-A7DE-A927331AE542}"/>
+    <hyperlink ref="J212" r:id="rId205" xr:uid="{B7D0E223-6F15-4B06-86E0-3CBBBC85B199}"/>
+    <hyperlink ref="J213" r:id="rId206" xr:uid="{7478D928-2004-4E0C-9632-AC49461C3AF2}"/>
+    <hyperlink ref="J214" r:id="rId207" xr:uid="{6E00A0A5-E858-4DBE-969C-98C026FB751B}"/>
+    <hyperlink ref="J215" r:id="rId208" display="https://www.nhmmaastricht.nl/" xr:uid="{BB226BDB-50A9-43CE-A855-14C5C524FA4A}"/>
+    <hyperlink ref="J216" r:id="rId209" display="https://www.etsu.edu/" xr:uid="{32FCDB6B-2E70-414D-A356-8C4A6FC734D6}"/>
+    <hyperlink ref="J217" r:id="rId210" display="https://www.uwsp.edu/" xr:uid="{BCE15A5F-63A9-4BCD-9992-F24CF57155A9}"/>
+    <hyperlink ref="J218" r:id="rId211" display="https://www.royalsaskmuseum.ca/" xr:uid="{E3F109AF-7738-49EA-8FC1-6EA400E9B6DA}"/>
+    <hyperlink ref="J219" r:id="rId212" display="https://www.tmag.tas.gov.au/" xr:uid="{65D428F3-272E-49E0-8C00-D1E4623559B8}"/>
+    <hyperlink ref="J220" r:id="rId213" xr:uid="{02E7E700-C8C8-4515-9D1D-589CEBDF276E}"/>
+    <hyperlink ref="J221" r:id="rId214" display="https://www.zzps.rs/" xr:uid="{C2569F0B-0E76-4ADD-961C-CB1019916EE0}"/>
+    <hyperlink ref="J222" r:id="rId215" xr:uid="{2E1E5A5D-47FD-462B-8420-7B6C83E99657}"/>
+    <hyperlink ref="J223" r:id="rId216" display="https://www.coe.edu/" xr:uid="{8EA2F305-0B83-4114-BB9C-D0B3B1549F71}"/>
+    <hyperlink ref="J224" r:id="rId217" xr:uid="{D7D3FE50-20C8-4031-856B-2867C7574B2A}"/>
+    <hyperlink ref="J225" r:id="rId218" display="https://www.pem.org/" xr:uid="{1069F33E-DBE7-4A5E-BAF4-7F46145F6032}"/>
+    <hyperlink ref="J226" r:id="rId219" display="https://www.isu.edu/" xr:uid="{7D0CE334-DB82-438E-A095-6F0B31BD97CB}"/>
+    <hyperlink ref="J227" r:id="rId220" display="https://museum.novascotia.ca/" xr:uid="{B4462A1B-AAA8-4C1C-A9E6-7A0C3E81E2B2}"/>
+    <hyperlink ref="J228" r:id="rId221" xr:uid="{5B0CB8E2-199D-453E-A94E-25C75374BDFE}"/>
+    <hyperlink ref="J229" r:id="rId222" display="https://www.fsu.edu/" xr:uid="{5731CF35-7574-4FBC-BE8C-4208174451DF}"/>
+    <hyperlink ref="J230" r:id="rId223" display="https://www.umaine.edu/" xr:uid="{9C400C61-9DA9-41E7-90B1-9844AC1C9542}"/>
+    <hyperlink ref="J231" r:id="rId224" display="https://www.museum-joanneum.at/" xr:uid="{76505AFF-B66E-4487-BAFE-FCD2DB423415}"/>
+    <hyperlink ref="J232" r:id="rId225" display="https://www.msn.unifi.it/" xr:uid="{590211C3-CB8A-4741-BAEB-1505240FAA3D}"/>
+    <hyperlink ref="J233" r:id="rId226" display="https://www.putnam.org/" xr:uid="{52D48778-4E9C-4F5F-9B58-393E37D706DD}"/>
+    <hyperlink ref="J234" r:id="rId227" xr:uid="{2531199A-01B7-47B2-BED7-2330CBE9FEAF}"/>
+    <hyperlink ref="J235" r:id="rId228" display="https://www.manitobamuseum.ca/" xr:uid="{44D15252-8E09-44E8-8F76-1DA20FD0A055}"/>
+    <hyperlink ref="J236" r:id="rId229" xr:uid="{C79C669E-532C-438B-AC4A-AA8DB94EF705}"/>
+    <hyperlink ref="J237" r:id="rId230" display="https://www.utm.edu/" xr:uid="{5C545861-095B-4257-BEF1-5A91E4D6FDFE}"/>
+    <hyperlink ref="J239" r:id="rId231" xr:uid="{8D1E9243-2C95-40D0-A218-2E5B42D4AA39}"/>
+    <hyperlink ref="J240" r:id="rId232" xr:uid="{5D451516-2728-4EC0-82BE-323E8B066B24}"/>
+    <hyperlink ref="J241" r:id="rId233" xr:uid="{49396B43-FF84-4A75-9A18-F3B5C6B09689}"/>
+    <hyperlink ref="J242" r:id="rId234" xr:uid="{B5FC5FCA-A2D5-4445-9104-2C65691E533D}"/>
+    <hyperlink ref="J243" r:id="rId235" xr:uid="{9A40CBD9-2255-447C-9B2B-F0C4A2101062}"/>
+    <hyperlink ref="J244" r:id="rId236" display="https://www.mnhn.lu/" xr:uid="{D2221EDF-1A1D-4BF2-9BEC-EDFAE9B49974}"/>
+    <hyperlink ref="J245" r:id="rId237" display="https://www.southendmuseums.co.uk/" xr:uid="{91E058EC-1B43-492D-935A-D34A7E5E9C17}"/>
+    <hyperlink ref="J246" r:id="rId238" display="https://museum.msu.edu/" xr:uid="{B8A83841-34DA-4036-9C85-980AF5CC313F}"/>
+    <hyperlink ref="J247" r:id="rId239" display="https://www.msstate.edu/" xr:uid="{82D62DE5-E73A-4FA6-B806-4ECDE9E57EA5}"/>
+    <hyperlink ref="J248" r:id="rId240" display="https://www.ecotarium.org/" xr:uid="{745F7214-BCEF-4785-9CCE-222910378700}"/>
+    <hyperlink ref="J249" r:id="rId241" display="https://www.fortworthmuseum.org/" xr:uid="{113AD817-E3D2-4CC4-90FE-C40AF105F8A4}"/>
+    <hyperlink ref="J250" r:id="rId242" xr:uid="{B388FA25-4308-4D0C-897D-8E0F24A2CD7F}"/>
+    <hyperlink ref="J251" r:id="rId243" xr:uid="{1E5D37ED-DD27-4982-A93A-BA696B4A8168}"/>
+    <hyperlink ref="J252" r:id="rId244" display="https://www.calstate.edu/" xr:uid="{94A40C82-AFEE-4A67-BDED-0FF460997EA3}"/>
+    <hyperlink ref="J253" r:id="rId245" display="https://www.sfasu.edu/" xr:uid="{DE58F494-F22A-40DE-AF93-75E92DA10BA4}"/>
+    <hyperlink ref="J254" r:id="rId246" display="https://www.wallawalla.edu/" xr:uid="{7E2760B3-7353-43E4-83C2-C21109B44C3C}"/>
+    <hyperlink ref="J255" r:id="rId247" display="https://www.museum-grenoble.fr/" xr:uid="{06375DDE-5C81-4C8F-91B1-4576EC200E73}"/>
+    <hyperlink ref="J256" r:id="rId248" display="https://www.vmo.cz/" xr:uid="{22FA1BE5-401A-4A03-8210-222F0D33AA1D}"/>
+    <hyperlink ref="J257" r:id="rId249" display="https://www.canterburymuseum.com/" xr:uid="{3A98C5EE-75CC-4DC2-9AA8-551781A99252}"/>
+    <hyperlink ref="J258" r:id="rId250" display="https://naturalhistory.si.edu/" xr:uid="{3521C4CE-08CE-4548-BC3C-6DC75AF7893F}"/>
+    <hyperlink ref="J259" r:id="rId251" display="https://www.cincymuseum.org/" xr:uid="{7D8F216B-15AA-4408-A2B4-A49421DBFFDB}"/>
+    <hyperlink ref="J260" r:id="rId252" display="https://www.colostate.edu/" xr:uid="{6CCF9BC0-F242-489D-9B20-F5FB1798D4D2}"/>
+    <hyperlink ref="J261" r:id="rId253" xr:uid="{0DDAFC51-D1EE-4C93-AF40-F5C642BE60BF}"/>
+    <hyperlink ref="J262" r:id="rId254" xr:uid="{32EEDB0A-7151-431F-84C3-0A78FEDE1565}"/>
+    <hyperlink ref="J263" r:id="rId255" display="https://www.mauritianum.de/" xr:uid="{6FBD19DD-4C7A-4D88-869E-43EB72C7EC79}"/>
+    <hyperlink ref="J264" r:id="rId256" display="https://www.swanseamuseum.co.uk/" xr:uid="{57DCCF63-8A62-492A-96AF-570E84BB909E}"/>
+    <hyperlink ref="J265" r:id="rId257" display="https://www.almnh.ua.edu/" xr:uid="{C068A00A-DCC4-4035-8523-6746CA864AD2}"/>
+    <hyperlink ref="J266" r:id="rId258" display="https://www.wagnerfreeinstitute.org/" xr:uid="{64497D0B-6510-42BD-B7B7-0D9BB98CF7E1}"/>
+    <hyperlink ref="J267" r:id="rId259" display="https://www.minotstateu.edu/" xr:uid="{9D0D290A-9FED-4765-A6AC-5C98AA77372B}"/>
+    <hyperlink ref="J268" r:id="rId260" display="https://www.sdstate.edu/" xr:uid="{C24E4273-E6AE-43DE-83F7-1CD2479959B3}"/>
+    <hyperlink ref="J269" r:id="rId261" xr:uid="{0B8448FA-7289-4CA3-B5C1-83F0B1D87D41}"/>
+    <hyperlink ref="J270" r:id="rId262" display="https://www.muzeumkarkonoskie.pl/" xr:uid="{76DF9BCA-1086-43A3-888D-EA4CF3C64AAF}"/>
+    <hyperlink ref="J271" r:id="rId263" display="https://www.yamashina.or.jp/" xr:uid="{C19152A4-18D9-4BCA-959F-70F3EEEC82CA}"/>
+    <hyperlink ref="J272" r:id="rId264" display="https://www.zin.ru/" xr:uid="{A26E8488-3D3F-4AF3-A04E-6E3B82AE766C}"/>
+    <hyperlink ref="J273" r:id="rId265" display="https://www.mncn.csic.es/" xr:uid="{22E4EB05-6F6E-413B-9BFA-106C4F366B9F}"/>
+    <hyperlink ref="J274" r:id="rId266" xr:uid="{30EF0216-4DCF-4DEF-9FB2-D12D0446F9FA}"/>
+    <hyperlink ref="J275" r:id="rId267" xr:uid="{C073D101-2D7F-45F6-A0DA-A863FDA369AC}"/>
+    <hyperlink ref="J276" r:id="rId268" display="https://www.tatmuseum.ru/" xr:uid="{57821D00-179E-4411-9334-1BEFDCD95D06}"/>
+    <hyperlink ref="J277" r:id="rId269" xr:uid="{B23BA6AF-5030-4672-AE53-B858A3CE2759}"/>
+    <hyperlink ref="J278" r:id="rId270" xr:uid="{B80C12A0-CC36-4F71-B8DC-3870A2C5D9EA}"/>
+    <hyperlink ref="J279" r:id="rId271" xr:uid="{839C1841-FCD3-420D-9B66-5BFAA0CC713B}"/>
+    <hyperlink ref="J280" r:id="rId272" xr:uid="{6DAD7A54-7AB2-48AF-AE4D-85F43C33D288}"/>
+    <hyperlink ref="J281" r:id="rId273" display="https://www.aquasis.org/" xr:uid="{41B6D3E9-EAEF-4ACC-871B-4B525EA4CF11}"/>
+    <hyperlink ref="J282" r:id="rId274" xr:uid="{4AC02F27-FDC2-43BD-A6C0-82B95B52FB53}"/>
+    <hyperlink ref="J284" r:id="rId275" xr:uid="{7F41AEC3-34E9-4D61-8FA6-772A8C8AAD00}"/>
+    <hyperlink ref="J286" r:id="rId276" xr:uid="{AFF4431E-8997-4736-AF92-991E2E333F21}"/>
+    <hyperlink ref="J287" r:id="rId277" xr:uid="{318600E6-E37C-463D-ABD6-31CBE8CF2EDE}"/>
+    <hyperlink ref="J288" r:id="rId278" xr:uid="{96319E3F-6980-48B5-B547-3B244FDF064F}"/>
+    <hyperlink ref="J289" r:id="rId279" xr:uid="{659403E8-C58D-4AB2-8CB5-39C5A149E45F}"/>
+    <hyperlink ref="J290" r:id="rId280" xr:uid="{B084A831-C16D-4947-BACF-57934931CCC1}"/>
+    <hyperlink ref="J291" r:id="rId281" xr:uid="{CC41AA84-81F3-4495-BA53-99E4F8A1D257}"/>
+    <hyperlink ref="J292" r:id="rId282" xr:uid="{C2B90B6A-6A51-462B-9FB1-D9A8193827E2}"/>
+    <hyperlink ref="J293" r:id="rId283" display="https://www.mnhn.cl/" xr:uid="{2E1A73C1-7D42-40D4-BE4E-B48DBEE29B46}"/>
+    <hyperlink ref="J295" r:id="rId284" xr:uid="{6EF55572-511F-4DBD-AA5D-27884B6E528A}"/>
+    <hyperlink ref="J296" r:id="rId285" xr:uid="{AB5D8B02-5010-421F-8B19-40E928610558}"/>
+    <hyperlink ref="J297" r:id="rId286" xr:uid="{79CC35A4-1B9A-467C-80A4-E901679E5836}"/>
+    <hyperlink ref="J299" r:id="rId287" display="https://www.magnt.net.au/" xr:uid="{BE273B34-F40C-4D07-B3EF-E1A5F16B5E9F}"/>
+    <hyperlink ref="J301" r:id="rId288" xr:uid="{6D80630C-6C67-4FC7-9048-EB9E02E873E7}"/>
+    <hyperlink ref="J302" r:id="rId289" xr:uid="{E0502669-408A-4C61-9F68-D6DA04AB90EE}"/>
+    <hyperlink ref="J303" r:id="rId290" display="https://www.dmns.org/" xr:uid="{FAA46BD7-4043-4191-9A0A-FCB4ADD1CA5B}"/>
+    <hyperlink ref="J305" r:id="rId291" display="https://samnoblemuseum.ou.edu/" xr:uid="{32AA8672-5C84-4ECE-AA75-5E4A93AB020A}"/>
+    <hyperlink ref="J306" r:id="rId292" xr:uid="{BACF6E96-4C19-4F8D-84C8-9EEDDF276375}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId282"/>
+  <pageSetup orientation="portrait" r:id="rId293"/>
 </worksheet>
 </file>